--- a/banks/ACCESS BANK UK FINANCIALS.xlsx
+++ b/banks/ACCESS BANK UK FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>The Access Bank UK Limited — Cash Flow Summary by Year</a:t>
+              <a:t>The Access Bank UK Limited — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -307,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -350,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +395,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>The Access Bank UK Limited — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>The Access Bank UK Limited — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>The Access Bank UK Limited — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -593,30 +1168,30 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q11</f>
+              <f>'Overview'!AO11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$AP$11:$AT$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -648,8 +1223,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -688,12 +1263,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -703,9 +1278,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -715,19 +1290,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1689,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,14 +1725,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£'000)</t>
+          <t>Balance Sheet Summary (£'000)</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1792,27 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2020</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
@@ -1156,273 +1821,273 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>914715.2</v>
+        <v>4894450.4</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>49148.5</v>
+        <v>3474169.2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>117981.6</v>
+        <v>3115077.7</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>455703.9</v>
+        <v>2281453.7</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-307926.5</v>
+        <v>1755034.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-307926.5</v>
+        <v>1755034.4</v>
       </c>
       <c r="K6" t="n">
-        <v>455703.9</v>
+        <v>2281453.7</v>
       </c>
       <c r="L6" t="n">
-        <v>117981.6</v>
+        <v>3115077.7</v>
       </c>
       <c r="M6" t="n">
-        <v>49148.5</v>
+        <v>3474169.2</v>
       </c>
       <c r="N6" t="n">
-        <v>914715.2</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>4894450.4</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>18.4</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>21.88</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>19.8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>22.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-1018064.7</v>
+        <v>1334233.8</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-250467.3</v>
+        <v>1196311.6</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-85936.39999999999</v>
+        <v>921615.8</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-184838.2</v>
+        <v>779823.3</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>46043.3</v>
+        <v>651852.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>46043.3</v>
+        <v>651852.8</v>
       </c>
       <c r="K7" t="n">
-        <v>-184838.2</v>
+        <v>779823.3</v>
       </c>
       <c r="L7" t="n">
-        <v>-85936.39999999999</v>
+        <v>921615.8</v>
       </c>
       <c r="M7" t="n">
-        <v>-250467.3</v>
+        <v>1196311.6</v>
       </c>
       <c r="N7" t="n">
-        <v>-1018064.7</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>1334233.8</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>18.4</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>21.88</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>19.8</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>22.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) financing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-22938.6</v>
+        <v>1238476.6</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>63364.5</v>
+        <v>1140155.1</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>51487.3</v>
+        <v>1035143.9</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-841.1</v>
+        <v>692107.4</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-1036.9</v>
+        <v>641605.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) financing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-1036.9</v>
+        <v>641605.3</v>
       </c>
       <c r="K8" t="n">
-        <v>-841.1</v>
+        <v>692107.4</v>
       </c>
       <c r="L8" t="n">
-        <v>51487.3</v>
+        <v>1035143.9</v>
       </c>
       <c r="M8" t="n">
-        <v>63364.5</v>
+        <v>1140155.1</v>
       </c>
       <c r="N8" t="n">
-        <v>-22938.6</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>1238476.6</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>18.4</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>21.88</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>19.8</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>22.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>241803</v>
+        <v>627171.1</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>364263.6</v>
+        <v>535897.1</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>524595.1</v>
+        <v>405955.2</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>392792.6</v>
+        <v>281638</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>117322.9</v>
+        <v>249045.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>117322.9</v>
+        <v>249045.8</v>
       </c>
       <c r="K9" t="n">
-        <v>392792.6</v>
+        <v>281638</v>
       </c>
       <c r="L9" t="n">
-        <v>524595.1</v>
+        <v>405955.2</v>
       </c>
       <c r="M9" t="n">
-        <v>364263.6</v>
+        <v>535897.1</v>
       </c>
       <c r="N9" t="n">
-        <v>241803</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>627171.1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>13.07</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>11.18</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>12</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>15.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>370.6</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>450.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>365.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Profit &amp; Loss Summary (£'000)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="AQ11" t="n">
         <v>196.8</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AR11" t="n">
         <v>147.9</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AS11" t="n">
         <v>168.6</v>
       </c>
     </row>
@@ -1457,177 +2122,826 @@
           <t>FY2020</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total operating income / Net operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>182688.1</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>160284.1</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>76210.8</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>63100.8</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>32870.6</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total operating income / Net operating income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>32870.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>63100.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>76210.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>160284.1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>182688.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expense</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-47037.5</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-38465.6</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-28726.6</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-25390.1</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-19761.1</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Total operating expense</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-19761.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-25390.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-28726.6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-38465.6</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-47037.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>99927.10000000001</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>90221.89999999999</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>36669.1</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>29447</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>10520.4</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>10520.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>29447</v>
+      </c>
+      <c r="T15" t="n">
+        <v>36669.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>90221.89999999999</v>
+      </c>
+      <c r="V15" t="n">
+        <v>99927.10000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>535897.1</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>405955.2</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>281638</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>249045.8</v>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>249045.8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>281638</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>405955.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>535897.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>98894.39999999999</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>91378.3</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>36629.5</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>29509.4</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>10331.9</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>10331.9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>29509.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>36629.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>91378.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>98894.39999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-18624.9</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>62347.9</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>52580.5</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>52580.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>62347.9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-18624.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>627171.1</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>535897.1</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>405955.2</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>281638</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>249045.8</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>249045.8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>281638</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>405955.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>535897.1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>627171.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>914715.2</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>49148.5</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>117981.6</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>455703.9</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-307926.5</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>-307926.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>455703.9</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>117981.6</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>49148.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>914715.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-1018064.7</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-250467.3</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-85936.39999999999</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-184838.2</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>46043.3</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>46043.3</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-184838.2</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-85936.39999999999</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-250467.3</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-1018064.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-22938.6</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>63364.5</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>51487.3</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-841.1</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1036.9</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>-1036.9</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-841.1</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>51487.3</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>63364.5</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-22938.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>241803</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>364263.6</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>524595.1</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>392792.6</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>117322.9</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>117322.9</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>392792.6</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>524595.1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>364263.6</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>241803</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>22.4%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>19.8%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>21.88%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>18.40%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>22.4%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>19.8%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>21.88%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>18.40%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>22.4%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>19.8%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>21.88%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>18.40%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>15.9%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>12.0%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>11.18%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>13.07%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>365.6%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>450.5%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>370.6%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>168.6%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>147.9%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>196.8%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n"/>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation. All £ figures are converted from the Bank's native USD reporting (see Cash Flow Statement sheet's FX conversion note) - this conversion was not explicitly requested for this bank but applied for consistency with the rest of the series. This workbook covers FY2020-FY2024 (shifted one year earlier than most other banks in this series) since no FY2025 Annual Report has been published yet; Pillar 3 cells are blank for FY2024 (no edition found) and FY2020 LCR/NSFR (not found in any source).</t>
+      <c r="F38" s="6" t="n"/>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation. All £ figures are converted from the Bank's native USD reporting (see Cash Flow Statement sheet's FX conversion note) - this conversion was not explicitly requested for this bank but applied for consistency with the rest of the series. This workbook covers FY2020-FY2024 (shifted one year earlier than most other banks in this series) since no FY2025 Annual Report has been published yet; Pillar 3 cells are blank for FY2024 (no edition found) and FY2020 LCR/NSFR (not found in any source). 'Total operating income / Net operating income' uses each year's Net operating income (after ECL), the one operating-income-level figure disclosed consistently across all 5 years (see Asset Quality sheet's presentation note on the P&amp;L structure change). Opening equity for FY2020 is not shown (no 31 December 2019 GBP/USD rate sourced) - see the Statement of Changes in Equity sheet's FX caveat.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1635,6 +2949,633 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 (conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>531687.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>402448.5</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>279437.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>248093.1</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Equal to CET1/Tier 1 capital in every year - the Bank holds no AT1 or Tier 2 instruments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 (conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>2375798.8</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2033020.6</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1277097.8</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1348332.5</v>
+      </c>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — RWA Breakdown (UK OV1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, converted from USD - see source note for FX methodology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts (RWEAs)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>2145347.2</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1850231.5</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1139061.5</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1223557.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>7696.4</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5454.2</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>619.8</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>6992.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Of which: credit valuation adjustment (CVA)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>1727.1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>684.5</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2567.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk (basic indicator approach)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>221028.9</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>177334.9</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>137268.7</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>115215.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n">
+        <v>2375798.8</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2033020.6</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1277097.8</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1348332.5</v>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited's own OV1 (Overview of risk weighted exposure amounts) table, converted from USD to £ at that year's BoE spot rate:
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 4.3, OV1) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 &amp; FY2020: Pillar 3 Disclosures 2022, p.15 (Section 4.3, OV1) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+No FY2024 Pillar 3 Disclosures document has been found (same gap already noted on the Pillar 3 metric sheets) - FY2024 cells are blank rather than guessed. The Bank has no market risk RWA requirement in any year shown (its own Pillar 3 reports state market risk is below the CRR de minimis threshold - it holds no trading book) - not a missing-disclosure gap, a genuine nil. 'Of which: credit valuation adjustment (CVA)' is a memo sub-item already included WITHIN 'Counterparty credit risk (CCR)' above it (per the OV1 template's own structure), not an additional component - it will appear to double-count against the Total row in a naive DATA-sum reconciliation check; this is expected and matches the Bank's own table structure.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:F11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1772,7 +3713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1922,7 +3863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2072,7 +4013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2196,6 +4137,1837 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, converted from USD, Bank basis - see source note at bottom for FX methodology and rates used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents / Cash at bank</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>241803</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>364263.6</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>524595.1</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>392792.6</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>117322.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Money market placements</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>10589.3</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>5622.5</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2976.3</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2905.5</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>4766.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Investment securities</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1833749.1</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>803837.1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>590237.8</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>451184.6</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>261076.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Investment in subsidiary</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>17757.9</v>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1418050.3</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1080914.2</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1049435.4</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>628250.8</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>690790.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1334233.8</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1196311.6</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>921615.8</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>779823.3</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>651852.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1623.8</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>894.2</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>904.7</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>698.3</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Right-of-use assets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>5831.2</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1938.3</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3167.7</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>3839.4</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>3551.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>6868.6</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3658.5</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3183.7</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1980.6</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1739.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Other financial/non-financial assets</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>20753.2</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>15213.9</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>18961.2</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>19978.7</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>23030.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Prepaid corporation tax</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>388.8</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>2801.5</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>1368.6</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>4894450.4</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3474169.2</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3115077.7</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2281453.7</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1755034.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Deposits from banks</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2972616.3</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1771700.8</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1654616.8</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1288483.6</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>842073</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Deposits from customers</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1238476.6</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1140155.1</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1035143.9</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>692107.4</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>641605.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>5807.9</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>1723.2</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Other financial/non-financial liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>40611.2</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>22374.6</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>18961.6</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>18847.6</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>22021.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax liability</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1780.7</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>944.5</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>400.2</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>289.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>7986.6</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>1373.8</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>4267279.3</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2938272.1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2709122.4</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1999815.7</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1505988.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>297547.1</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>292475.8</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>225163.5</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>153376.4</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>151804.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>333698.6</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>246389.6</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>185105.1</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>132084.4</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>101087.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>-68.59999999999999</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>969.4</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>-168.8</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>-114.8</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-176.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Currency translation reserve</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-4006</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-3937.8</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>-4144.5</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>-3708</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-3670</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>627171.1</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>535897.1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>405955.2</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>281638</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>249045.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>4894450.4</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>3474169.2</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3115077.7</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>2281453.7</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1755034.4</v>
+      </c>
+    </row>
+    <row r="34" ht="260" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited's own Statement of Financial Position (Bank column), converted from USD to £ per the FX conversion note on the Cash Flow Statement sheet:
+FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, p.21 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+FY2022 &amp; FY2021: Report and Statutory Accounts 2022, p.17 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
+FY2020: Report and Statutory Accounts 2021, p.15 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+PRESENTATION NOTE: The Bank column (entity-level) is used throughout for consistency with the Cash Flow Statement sheet - Bank and Group are identical for FY2020-FY2023 (no subsidiary existed) and differ only immaterially for FY2024 (following the Access Bank Malta investment - see Investment in Subsidiary note). The Balance Sheet's line-item structure changed between report vintages: FY2024/FY2023 (AR2024) present 'Money market placements', 'Investment in subsidiary', 'Deferred tax liability' and a 'Prepaid corporation tax' asset as separate lines not present in earlier years; FY2022 (AR2022)/FY2021/FY2020 group these differently (e.g. a single 'Cash at bank' line, no separate money-market-placements or investment-securities split visible pre-FY2021 in the same granularity). Each year's own as-reported labels/granularity are preserved rather than forced into a common shape - blank cells indicate that year's report did not disclose that specific line. The P&amp;L's structure also changed: FY2024/FY2023 use a 'Total operating income' / 'Net operating income' (after ECL) structure; FY2022/FY2021/FY2020 use a similar shape but without the 'Total operating income' subtotal line (ECL is deducted one step later, after 'Other income', directly into 'Net operating income').</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A34:F34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Statement of Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, converted from USD, Bank basis - see source note at bottom for FX methodology and rates used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>283516.2</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>220405.3</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>105009.8</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>73510.8</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>76400.89999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-120537.4</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-80724.7</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-24532.6</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-12787.8</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-19140.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>162978.8</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>139680.5</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>80477.2</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>60723</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>25613.9</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>24611.7</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>24246.4</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>19737.6</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>20833.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission expense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-2262.2</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-1448.9</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-1614.3</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-1345.9</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-951.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee and commission income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>23351.7</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>23162.8</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>22632.1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>18391.7</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>19881.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>4834.3</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4056.8</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>3251.4</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1726.2</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1406.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n">
+        <v>5869.8</v>
+      </c>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>191164.7</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>166900.1</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Expected credit loss (ECL) allowance / Provision for expected credit losses</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-8476.6</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-6616.1</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-30149.9</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-23609.8</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-45677.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>182688.1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>160284.1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>76210.8</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>63100.8</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>32870.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Personnel expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-30320.3</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-25622.8</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-18183.2</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-16270.7</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-13286.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-3258.1</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-2057.3</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-1850.7</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-1387.3</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-1798.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-13459</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-10785.5</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-8692.6</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-7732.1</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-4676.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-47037.5</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-38465.6</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-28726.6</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-25390.1</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-19761.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Profit before tax expense</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>135650.6</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>121818.5</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>47484.2</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>37710.8</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>13109.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Tax expense / Taxation</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>-35723.5</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-31596.5</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-10815.2</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>-8263.799999999999</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-2589.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Profit after tax expense for the year</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>99927.10000000001</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>90221.89999999999</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>36669.1</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>29447</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>10520.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(expense)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income on investment securities / net profit on FVOCI securities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>-1032.8</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>1156.4</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-188.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>98894.39999999999</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>91378.3</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>36629.5</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>29509.4</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>10331.9</v>
+      </c>
+    </row>
+    <row r="28" ht="260" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited's own Statement of Comprehensive Income (Bank column), converted from USD to £ per the FX conversion note on the Cash Flow Statement sheet:
+FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, p.20 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+FY2022 &amp; FY2021: Report and Statutory Accounts 2022, p.16 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
+FY2020: Report and Statutory Accounts 2021, p.14 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+PRESENTATION NOTE: The Bank column (entity-level) is used throughout for consistency with the Cash Flow Statement sheet - Bank and Group are identical for FY2020-FY2023 (no subsidiary existed) and differ only immaterially for FY2024 (following the Access Bank Malta investment - see Investment in Subsidiary note). The Balance Sheet's line-item structure changed between report vintages: FY2024/FY2023 (AR2024) present 'Money market placements', 'Investment in subsidiary', 'Deferred tax liability' and a 'Prepaid corporation tax' asset as separate lines not present in earlier years; FY2022 (AR2022)/FY2021/FY2020 group these differently (e.g. a single 'Cash at bank' line, no separate money-market-placements or investment-securities split visible pre-FY2021 in the same granularity). Each year's own as-reported labels/granularity are preserved rather than forced into a common shape - blank cells indicate that year's report did not disclose that specific line. The P&amp;L's structure also changed: FY2024/FY2023 use a 'Total operating income' / 'Net operating income' (after ECL) structure; FY2022/FY2021/FY2020 use a similar shape but without the 'Total operating income' subtotal line (ECL is deducted one step later, after 'Other income', directly into 'Net operating income').</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A28:F28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, converted from USD, Bank basis - chronological, oldest to newest. See source note for FX methodology/caveat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Currency translation reserve</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 1 January 2020</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax for the year (2020)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>10520.4</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>10520.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive expense for the year (2020)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-188.5</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-188.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (2020)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>10520.4</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-188.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>10331.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2020</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>151804.6</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>101087.6</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-176.4</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3670</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>249045.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax for the year (2021)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>29447</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>29447</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income for the year (2021)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (2021)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>29447</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>29509.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>153376.4</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>132084.4</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-114.8</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-3708</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>281638</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax for the year (2022)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>36669.1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>36669.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive expense for the year (2022)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-39.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (2022)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>36669.1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>36629.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Proceeds from shares issued (2022)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>52580.5</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>52580.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>225163.5</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>185105.1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-168.8</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4144.5</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>405955.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax for the year (2023)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>90221.89999999999</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>90221.89999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income for the year (2023)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1156.4</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1156.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (2023)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>90221.89999999999</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1156.4</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>91378.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Proceeds from shares issued (2023)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>80392.3</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>80392.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Dividends declared (2023)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-18044.4</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-18044.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>292475.8</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>246389.6</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>969.4</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3937.8</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>535897.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax for the year (2024)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>99927.10000000001</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>99927.10000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive expense for the year (2024)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-1032.8</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-1032.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (2024)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>99927.10000000001</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-1032.8</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>98894.39999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Dividends declared (2024)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>-18624.9</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-18624.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>297547.1</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>333698.6</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-68.59999999999999</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-4006</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>627171.1</v>
+      </c>
+    </row>
+    <row r="30" ht="280" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited's own Statement of Changes in Equity (Bank basis), converted from USD to £ (Balance rows at that date's BoE spot rate; movement rows at that calendar year's BoE average rate - same FX methodology as the Cash Flow Statement sheet):
+2024 &amp; 2023 movements: Report &amp; Financial Statements 2024, p.22 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+2022 &amp; 2021 movements: Report and Statutory Accounts 2022, p.18 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
+2020 movements: Report and Statutory Accounts 2021, p.16 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+EQUITY SHEET FX CAVEAT: because this roll-forward mixes point-in-time Balance rows (spot rate) with in-year movement rows (average rate) - the same two-rate approach used for the Cash Flow Statement - each period's £ closing balance will differ very slightly from £ opening balance + £ movements (unlike the Cash Flow Statement, this sheet has no natural 'FX translation' line to absorb the difference, so no plug row is shown here). The underlying USD figures (see rows above) tie out exactly in every period; this is purely a £ presentation artefact of using two different conversion rates, not a data quality issue.
+PRESENTATION NOTE: The Balance as at 1 January 2020 row is left blank (not converted) since it would require a 31 December 2019 GBP/USD spot rate, which hasn't been sourced for this project - matching the same gap already noted for the Cash Flow Statement's FY2020 opening balance. FY2022's own statement labels its 'Proceeds from shares issued' row as part of a combined 'Total comprehensive income for the year' total (which would overstate that label); this workbook instead reports 'Total comprehensive income for the year (2022)' as profit + OCI only (excluding the share issuance), with 'Proceeds from shares issued' shown as its own separate row immediately after - the Balance at 31 December 2022 row still ties to the sum of all rows in between, this is a relabeling for clarity only, not a change to any figure.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A30:F30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2922,7 +6694,517 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Asset Quality / Credit Risk Disclosures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, converted from USD, Group basis - see source note for FX methodology and product/stage basis caveats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loan book by product/segment (basis differs by year - see presentation note)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Loans to corporates (gross)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1188676.1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1089045.5</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Loans secured on property (gross)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>103036.6</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>94673.7</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Other secured personal loans (gross)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>64148.3</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>33315.4</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Retail loans, incl. mortgages (net of allowance)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n">
+        <v>125256.2</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>108776.4</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>80363.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Corporate loans, incl. mortgages (net of allowance)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n">
+        <v>796359.6</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>671046.8</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>571489.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Total loans and advances to customers (gross FY2023-24 / net FY2020-22)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1355861</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1217034.6</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>921615.8</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>779823.3</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>651852.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Loan book by IFRS 9 stage (gross carrying amount)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 (12-month ECL)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1239505.3</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1138323.6</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>855651.4</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>686246.6</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>540993.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 (lifetime ECL, not credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>45984</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>9539.6</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>8887.700000000001</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>11889.2</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>70874.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (lifetime ECL, credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>70371.7</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>69171.39999999999</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>93186.60000000001</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>137044.6</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>82761</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total gross carrying amount</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1355861</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1217034.6</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>957725.7</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>835180.4</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>694628.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Loss allowance by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 loss allowance</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-1089</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-843</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-641.3</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-360</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-539.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 loss allowance</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-20306.5</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-32.6</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-6385.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 loss allowance</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-231.7</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-19880</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-35453.4</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-54964.5</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-35851.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total loss allowance</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-21627.2</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-20723</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-36109.9</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-55357.1</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-42775.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Asset quality ratios (computed from the £-converted figures above)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ECL coverage ratio (total loss allowance / total gross carrying amount)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 / NPL ratio (Stage 3 gross / total gross carrying amount)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>5.7%</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>11.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 coverage ratio (Stage 3 loss allowance / Stage 3 gross)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>28.7%</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>38.0%</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>40.1%</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>43.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="300" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited's own Note 27/24 'Financial instruments - Credit risk' (Group basis; immaterially different from Bank basis in every year - see entity note), converted from USD to £ at that year's BoE spot rate (point-in-time balances, same as the Balance Sheet sheet's convention):
+FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, p.51-52 (Note 27d, Loans to customers ECL staging table) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+FY2022 &amp; FY2021: Report and Statutory Accounts 2022, p.43 (Note 24d) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
+FY2020: Report and Statutory Accounts 2021, p.42 (Note 24d, comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+PRESENTATION NOTE: the loan-book-by-product split is NOT presented on a consistent basis across all 5 years - FY2024/FY2023 disclose a GROSS product split (Loans to corporates / secured on property / other secured personal loans, from Note 18/17); FY2022/FY2021/FY2020 only disclose a NET-of-allowance Retail/Corporate split (from the credit risk exposure table), not a gross one at that granularity - each row is labelled to make this explicit, and the 'Total loans and advances to customers' row for each year sums exactly to whichever rows are populated for that year (gross FY2023-24, net FY2020-22) - do not compare that total row directly across the gross/net boundary. The by-IFRS-9-stage breakdown below IS on a consistent gross basis for all 5 years and ties to each year's own Balance Sheet 'Loans and advances to customers' gross figure. FY2024's Stage 3 loss allowance coverage (0.3%) is much lower than FY2023's (28.7%) - both figures are as directly reported; the Bank's own notes attribute this to a large trade-finance Stage 3 exposure ($49.9m) that is substantially collateralised by credit insurance, so most of its gross balance is not provisioned for - flagged here for visibility rather than smoothed over.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A26:F26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3019,446 +7301,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>21.88%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000 (conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>531687.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>402448.5</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>279437.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>248093.1</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Equal to CET1 capital in every year - the Bank holds no Additional Tier 1 (AT1) instruments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="130" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>21.88%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Total Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000 (conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>531687.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>402448.5</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>279437.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>248093.1</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Equal to CET1/Tier 1 capital in every year - the Bank holds no AT1 or Tier 2 instruments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="130" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3484,7 +7326,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — Total Capital Ratio</t>
+          <t>The Access Bank UK Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3530,7 +7372,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -3580,7 +7422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3594,7 +7436,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — Total RWAs</t>
+          <t>The Access Bank UK Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3640,25 +7482,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n">
-        <v>2375798.8</v>
+        <v>531687.1</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2033020.6</v>
+        <v>402448.5</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1277097.8</v>
+        <v>279437.2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1348332.5</v>
-      </c>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+        <v>248093.1</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Equal to CET1 capital in every year - the Bank holds no Additional Tier 1 (AT1) instruments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
 FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
@@ -3669,8 +7518,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/ACCESS BANK UK FINANCIALS.xlsx
+++ b/banks/ACCESS BANK UK FINANCIALS.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -197,13 +197,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -236,22 +236,22 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!I6</f>
+              <f>'Overview'!J6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$K$5:$P$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$6:$N$6</f>
+              <f>'Overview'!$K$6:$P$6</f>
             </numRef>
           </val>
         </ser>
@@ -260,22 +260,22 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!I7</f>
+              <f>'Overview'!J7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$K$5:$P$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$7:$N$7</f>
+              <f>'Overview'!$K$7:$P$7</f>
             </numRef>
           </val>
         </ser>
@@ -284,22 +284,22 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!I8</f>
+              <f>'Overview'!J8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$K$5:$P$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$8:$N$8</f>
+              <f>'Overview'!$K$8:$P$8</f>
             </numRef>
           </val>
         </ser>
@@ -308,22 +308,22 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!I9</f>
+              <f>'Overview'!J9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$K$5:$P$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$9:$N$9</f>
+              <f>'Overview'!$K$9:$P$9</f>
             </numRef>
           </val>
         </ser>
@@ -355,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -395,13 +395,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -434,22 +434,22 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q13</f>
+              <f>'Overview'!S13</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$T$12:$Y$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$13:$V$13</f>
+              <f>'Overview'!$T$13:$Y$13</f>
             </numRef>
           </val>
         </ser>
@@ -458,22 +458,22 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q14</f>
+              <f>'Overview'!S14</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$T$12:$Y$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$14:$V$14</f>
+              <f>'Overview'!$T$14:$Y$14</f>
             </numRef>
           </val>
         </ser>
@@ -482,22 +482,22 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q15</f>
+              <f>'Overview'!S15</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$T$12:$Y$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$15:$V$15</f>
+              <f>'Overview'!$T$15:$Y$15</f>
             </numRef>
           </val>
         </ser>
@@ -529,8 +529,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,13 +569,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -608,22 +608,22 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y19</f>
+              <f>'Overview'!AB19</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AC$18:$AH$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$19:$AD$19</f>
+              <f>'Overview'!$AC$19:$AH$19</f>
             </numRef>
           </val>
         </ser>
@@ -632,22 +632,22 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y20</f>
+              <f>'Overview'!AB20</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AC$18:$AH$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$20:$AD$20</f>
+              <f>'Overview'!$AC$20:$AH$20</f>
             </numRef>
           </val>
         </ser>
@@ -656,22 +656,22 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y21</f>
+              <f>'Overview'!AB21</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AC$18:$AH$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$21:$AD$21</f>
+              <f>'Overview'!$AC$21:$AH$21</f>
             </numRef>
           </val>
         </ser>
@@ -680,22 +680,22 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y22</f>
+              <f>'Overview'!AB22</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AC$18:$AH$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$22:$AD$22</f>
+              <f>'Overview'!$AC$22:$AH$22</f>
             </numRef>
           </val>
         </ser>
@@ -727,8 +727,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -767,13 +767,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -806,22 +806,22 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG26</f>
+              <f>'Overview'!AK26</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AL$25:$AQ$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$26:$AL$26</f>
+              <f>'Overview'!$AL$26:$AQ$26</f>
             </numRef>
           </val>
         </ser>
@@ -830,22 +830,22 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG27</f>
+              <f>'Overview'!AK27</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AL$25:$AQ$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$27:$AL$27</f>
+              <f>'Overview'!$AL$27:$AQ$27</f>
             </numRef>
           </val>
         </ser>
@@ -854,22 +854,22 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG28</f>
+              <f>'Overview'!AK28</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AL$25:$AQ$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$28:$AL$28</f>
+              <f>'Overview'!$AL$28:$AQ$28</f>
             </numRef>
           </val>
         </ser>
@@ -878,22 +878,22 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG29</f>
+              <f>'Overview'!AK29</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AL$25:$AQ$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$29:$AL$29</f>
+              <f>'Overview'!$AL$29:$AQ$29</f>
             </numRef>
           </val>
         </ser>
@@ -925,8 +925,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -965,13 +965,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1003,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO6</f>
+              <f>'Overview'!AT6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$6:$AT$6</f>
+              <f>'Overview'!$AU$6:$AZ$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1036,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO7</f>
+              <f>'Overview'!AT7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$7:$AT$7</f>
+              <f>'Overview'!$AU$7:$AZ$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1069,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO8</f>
+              <f>'Overview'!AT8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$8:$AT$8</f>
+              <f>'Overview'!$AU$8:$AZ$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1102,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO9</f>
+              <f>'Overview'!AT9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$9:$AT$9</f>
+              <f>'Overview'!$AU$9:$AZ$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1135,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO10</f>
+              <f>'Overview'!AT10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$10:$AT$10</f>
+              <f>'Overview'!$AU$10:$AZ$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1168,30 +1168,30 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO11</f>
+              <f>'Overview'!AT11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$AU$5:$AZ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$11:$AT$11</f>
+              <f>'Overview'!$AU$11:$AZ$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1223,8 +1223,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1263,7 +1263,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1278,9 +1278,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1300,9 +1300,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1322,9 +1322,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1344,9 +1344,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1366,9 +1366,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1666,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1675,7 +1675,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
@@ -1713,6 +1713,12 @@
     <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
     <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
+    <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col hidden="1" width="13" customWidth="1" min="48" max="48"/>
+    <col hidden="1" width="13" customWidth="1" min="49" max="49"/>
+    <col hidden="1" width="13" customWidth="1" min="50" max="50"/>
+    <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
+    <col hidden="1" width="13" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1767,52 +1773,67 @@
           <t>FY2020</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>FY2020</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>FY2020</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
@@ -1839,42 +1860,46 @@
       <c r="F6" s="5" t="n">
         <v>1755034.4</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>1755034.4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>2281453.7</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>3115077.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>3474169.2</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>4894450.4</v>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AV6" t="n">
         <v>18.4</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AW6" t="n">
         <v>21.88</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AX6" t="n">
         <v>19.8</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AY6" t="n">
         <v>22.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20.18</v>
       </c>
     </row>
     <row r="7">
@@ -1898,42 +1923,46 @@
       <c r="F7" s="5" t="n">
         <v>651852.8</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="5" t="n"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Loans and advances to customers</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>651852.8</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>779823.3</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>921615.8</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>1196311.6</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>1334233.8</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AV7" t="n">
         <v>18.4</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AW7" t="n">
         <v>21.88</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AX7" t="n">
         <v>19.8</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AY7" t="n">
         <v>22.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>20.18</v>
       </c>
     </row>
     <row r="8">
@@ -1957,42 +1986,46 @@
       <c r="F8" s="5" t="n">
         <v>641605.3</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Customer deposits</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>641605.3</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>692107.4</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>1035143.9</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>1140155.1</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>1238476.6</v>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AV8" t="n">
         <v>18.4</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AW8" t="n">
         <v>21.88</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AX8" t="n">
         <v>19.8</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AY8" t="n">
         <v>22.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>20.18</v>
       </c>
     </row>
     <row r="9">
@@ -2016,58 +2049,62 @@
       <c r="F9" s="5" t="n">
         <v>249045.8</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>249045.8</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>281638</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>405955.2</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>535897.1</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>627171.1</v>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AV9" t="n">
         <v>13.07</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AW9" t="n">
         <v>11.18</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AX9" t="n">
         <v>12</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AY9" t="n">
         <v>15.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="AO10" t="inlineStr">
+      <c r="AT10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AW10" t="n">
         <v>370.6</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AX10" t="n">
         <v>450.5</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AY10" t="n">
         <v>365.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>176.65</v>
       </c>
     </row>
     <row r="11">
@@ -2076,18 +2113,18 @@
           <t>Profit &amp; Loss Summary (£'000)</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AW11" t="n">
         <v>196.8</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AX11" t="n">
         <v>147.9</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AY11" t="n">
         <v>168.6</v>
       </c>
     </row>
@@ -2122,27 +2159,37 @@
           <t>FY2020</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>FY2020</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
@@ -2169,24 +2216,25 @@
       <c r="F13" s="5" t="n">
         <v>32870.6</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="S13" t="inlineStr">
         <is>
           <t>Total operating income / Net operating income</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>32870.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>63100.8</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>76210.8</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>160284.1</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>182688.1</v>
       </c>
     </row>
@@ -2211,24 +2259,25 @@
       <c r="F14" s="5" t="n">
         <v>-19761.1</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Total operating expense</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>-19761.1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>-25390.1</v>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>-28726.6</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>-38465.6</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
         <v>-47037.5</v>
       </c>
     </row>
@@ -2253,24 +2302,25 @@
       <c r="F15" s="5" t="n">
         <v>10520.4</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="G15" s="5" t="n"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>10520.4</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>29447</v>
       </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
         <v>36669.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>90221.89999999999</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>99927.10000000001</v>
       </c>
     </row>
@@ -2312,27 +2362,37 @@
           <t>FY2020</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>FY2020</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
@@ -2357,21 +2417,22 @@
         <v>249045.8</v>
       </c>
       <c r="F19" s="5" t="n"/>
-      <c r="Y19" t="inlineStr">
+      <c r="G19" s="5" t="n"/>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Opening equity</t>
         </is>
       </c>
-      <c r="AA19" t="n">
+      <c r="AE19" t="n">
         <v>249045.8</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AF19" t="n">
         <v>281638</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AG19" t="n">
         <v>405955.2</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AH19" t="n">
         <v>535897.1</v>
       </c>
     </row>
@@ -2396,24 +2457,25 @@
       <c r="F20" s="5" t="n">
         <v>10331.9</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>Total comprehensive income for the year</t>
         </is>
       </c>
-      <c r="Z20" t="n">
+      <c r="AD20" t="n">
         <v>10331.9</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AE20" t="n">
         <v>29509.4</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AF20" t="n">
         <v>36629.5</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AG20" t="n">
         <v>91378.3</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AH20" t="n">
         <v>98894.39999999999</v>
       </c>
     </row>
@@ -2438,24 +2500,25 @@
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>Other equity movements, net</t>
         </is>
       </c>
-      <c r="Z21" t="n">
+      <c r="AD21" t="n">
         <v>0</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AE21" t="n">
         <v>0</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AF21" t="n">
         <v>52580.5</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AG21" t="n">
         <v>62347.9</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AH21" t="n">
         <v>-18624.9</v>
       </c>
     </row>
@@ -2480,24 +2543,25 @@
       <c r="F22" s="5" t="n">
         <v>249045.8</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>Closing equity</t>
         </is>
       </c>
-      <c r="Z22" t="n">
+      <c r="AD22" t="n">
         <v>249045.8</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AE22" t="n">
         <v>281638</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
         <v>405955.2</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AG22" t="n">
         <v>535897.1</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AH22" t="n">
         <v>627171.1</v>
       </c>
     </row>
@@ -2539,27 +2603,37 @@
           <t>FY2020</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
         <is>
           <t>FY2020</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AP25" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AQ25" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
@@ -2586,24 +2660,25 @@
       <c r="F26" s="5" t="n">
         <v>-307926.5</v>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="G26" s="5" t="n"/>
+      <c r="AK26" t="inlineStr">
         <is>
           <t>Net cash from/(used in) operating activities</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="AM26" t="n">
         <v>-307926.5</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AN26" t="n">
         <v>455703.9</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AO26" t="n">
         <v>117981.6</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AP26" t="n">
         <v>49148.5</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AQ26" t="n">
         <v>914715.2</v>
       </c>
     </row>
@@ -2628,24 +2703,25 @@
       <c r="F27" s="5" t="n">
         <v>46043.3</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="G27" s="5" t="n"/>
+      <c r="AK27" t="inlineStr">
         <is>
           <t>Net cash from/(used in) investing activities</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="AM27" t="n">
         <v>46043.3</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AN27" t="n">
         <v>-184838.2</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AO27" t="n">
         <v>-85936.39999999999</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AP27" t="n">
         <v>-250467.3</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AQ27" t="n">
         <v>-1018064.7</v>
       </c>
     </row>
@@ -2670,24 +2746,25 @@
       <c r="F28" s="5" t="n">
         <v>-1036.9</v>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="G28" s="5" t="n"/>
+      <c r="AK28" t="inlineStr">
         <is>
           <t>Net cash from/(used in) financing activities</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="AM28" t="n">
         <v>-1036.9</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AN28" t="n">
         <v>-841.1</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AO28" t="n">
         <v>51487.3</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AP28" t="n">
         <v>63364.5</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AQ28" t="n">
         <v>-22938.6</v>
       </c>
     </row>
@@ -2712,24 +2789,25 @@
       <c r="F29" s="5" t="n">
         <v>117322.9</v>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="G29" s="5" t="n"/>
+      <c r="AK29" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of year</t>
         </is>
       </c>
-      <c r="AH29" t="n">
+      <c r="AM29" t="n">
         <v>117322.9</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AN29" t="n">
         <v>392792.6</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AO29" t="n">
         <v>524595.1</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AP29" t="n">
         <v>364263.6</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AQ29" t="n">
         <v>241803</v>
       </c>
     </row>
@@ -2771,6 +2849,11 @@
           <t>FY2020</t>
         </is>
       </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2778,7 +2861,11 @@
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
           <t>22.4%</t>
@@ -2799,6 +2886,7 @@
           <t>18.40%</t>
         </is>
       </c>
+      <c r="G33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2806,7 +2894,11 @@
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
           <t>22.4%</t>
@@ -2827,6 +2919,7 @@
           <t>18.40%</t>
         </is>
       </c>
+      <c r="G34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2834,7 +2927,11 @@
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
           <t>22.4%</t>
@@ -2855,6 +2952,7 @@
           <t>18.40%</t>
         </is>
       </c>
+      <c r="G35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2883,6 +2981,7 @@
           <t>13.07%</t>
         </is>
       </c>
+      <c r="G36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -2890,7 +2989,11 @@
           <t>LCR</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>176.65%</t>
+        </is>
+      </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
           <t>365.6%</t>
@@ -2907,6 +3010,7 @@
         </is>
       </c>
       <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2931,6 +3035,7 @@
         </is>
       </c>
       <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
@@ -2941,7 +3046,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2954,7 +3059,2637 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 (conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>531687.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>402448.5</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>279437.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>248093.1</v>
+      </c>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Equal to CET1/Tier 1 capital in every year - the Bank holds no AT1 or Tier 2 instruments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 (conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>2375798.8</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2033020.6</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1277097.8</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1348332.5</v>
+      </c>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — RWA Breakdown (UK OV1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, converted from USD - see source note for FX methodology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts (RWEAs)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>2145347.2</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1850231.5</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1139061.5</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1223557.6</v>
+      </c>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>7696.4</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5454.2</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>619.8</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>6992.2</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Of which: credit valuation adjustment (CVA)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>1727.1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>684.5</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2567.2</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk (basic indicator approach)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>221028.9</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>177334.9</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>137268.7</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>115215.6</v>
+      </c>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n">
+        <v>2375798.8</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2033020.6</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1277097.8</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1348332.5</v>
+      </c>
+      <c r="G9" s="5" t="n"/>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited's own OV1 (Overview of risk weighted exposure amounts) table, converted from USD to £ at that year's BoE spot rate:
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 4.3, OV1) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 &amp; FY2020: Pillar 3 Disclosures 2022, p.15 (Section 4.3, OV1) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2019-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+No FY2024 Pillar 3 Disclosures document has been found (same gap already noted on the Pillar 3 metric sheets) - FY2024 cells are blank rather than guessed. The Bank has no market risk RWA requirement in any year shown (its own Pillar 3 reports state market risk is below the CRR de minimis threshold - it holds no trading book) - not a missing-disclosure gap, a genuine nil. 'Of which: credit valuation adjustment (CVA)' is a memo sub-item already included WITHIN 'Counterparty credit risk (CCR)' above it (per the OV1 template's own structure), not an additional component - it will appear to double-count against the Total row in a naive DATA-sum reconciliation check; this is expected and matches the Bank's own table structure.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:G11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Leverage Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 / % (conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total exposure measure</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>3335479.9</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3357849.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2499781.8</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1899792.8</v>
+      </c>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>15.9%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>11.18%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>13.07%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2020/FY2021 source tables (UK LR2, in the FY2021 Pillar 3 report) label this 'including claims on central banks'; FY2022 onward (UK KM1 template) labels it 'excluding claims on central banks'. Despite the differing labels, the FY2021 figure is identical (3,379,955) in both the FY2021 report's own table and the FY2022 report's comparative column, so this appears to be inconsistent wording by the Bank rather than a genuine methodology change - shown here as a single continuous row, flagged for visibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="130" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 / % (conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total high-quality liquid assets (HQLA), weighted value</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>708481</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>870655.5</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>596938.8</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total net cash outflows, adjusted value</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>193806.2</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>193268.6</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>161053.2</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>176.65%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>365.6%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>450.5%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>370.6%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021's $ breakdown (HQLA/net cash outflows) is sourced from the FY2022 Pillar 3 report's comparative column - the FY2021 Pillar 3 report itself only states a single narrative LCR percentage (343.9%, a slightly different figure from the 370.6% shown here), not a KM1-style table with a $ breakdown. The two FY2021 percentages differ slightly, most likely because the narrative figure is a different point-in-time/averaging convention than the KM1 template's 'average of preceding twelve months' basis used here - both are the Bank's own disclosures, this workbook uses the KM1-consistent figure. FY2020 not found in any source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="130" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 / % (conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>1475757.9</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1213379.4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1318835.1</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>875261.5</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>820509.2</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>670287.7</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>168.6%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>147.9%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>196.8%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021's $ breakdown is sourced from the FY2022 Pillar 3 report's comparative column (the FY2021 report itself does not tabulate NSFR). FY2020 not found in any source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="130" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: No MREL disclosure (numeric or qualitative) or UK KM2 template found in any year's Pillar 3 report - not explicitly stated as an exemption, but consistent with the Bank's small size relative to typical MREL-in-scope thresholds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, converted from USD, Bank basis - see source note at bottom for FX methodology and rates used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents / Cash at bank</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>241803</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>364263.6</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>524595.1</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>392792.6</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>117322.9</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>376653.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Money market placements</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>10589.3</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>5622.5</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2976.3</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2905.5</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>4766.1</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>17592.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Investment securities</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1833749.1</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>803837.1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>590237.8</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>451184.6</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>261076.9</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>315762.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Investment in subsidiary</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>17757.9</v>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1418050.3</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1080914.2</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1049435.4</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>628250.8</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>690790.5</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>510453.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1334233.8</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1196311.6</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>921615.8</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>779823.3</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>651852.8</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>661685.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1623.8</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>894.2</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>904.7</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>698.3</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>904</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>2095.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Right-of-use assets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>5831.2</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1938.3</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3167.7</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>3839.4</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>3551.3</v>
+      </c>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>6868.6</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>3658.5</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3183.7</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1980.6</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1739.7</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1899.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Other financial/non-financial assets</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>20753.2</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>15213.9</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>18961.2</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>19978.7</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>23030.2</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>6059.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Prepaid corporation tax</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>388.8</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>2801.5</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>1368.6</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>4894450.4</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3474169.2</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3115077.7</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2281453.7</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1755034.4</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1892202.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Deposits from banks</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2972616.3</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1771700.8</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1654616.8</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1288483.6</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>842073</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>1027714.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Deposits from customers</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1238476.6</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1140155.1</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1035143.9</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>692107.4</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>641605.3</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>591188.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>5807.9</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>1723.2</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Other financial/non-financial liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>40611.2</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>22374.6</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>18961.6</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>18847.6</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>22021.1</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>25614.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax liability</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1780.7</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>944.5</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>400.2</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>289.2</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>176.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>7986.6</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>1373.8</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>4267279.3</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2938272.1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2709122.4</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1999815.7</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1505988.6</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1644694.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>297547.1</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>292475.8</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>225163.5</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>153376.4</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>151804.6</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>156987.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>333698.6</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>246389.6</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>185105.1</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>132084.4</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>101087.6</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>94315.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>-68.59999999999999</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>969.4</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>-168.8</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>-114.8</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-176.4</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Currency translation reserve</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-4006</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-3937.8</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>-4144.5</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>-3708</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-3670</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>-3795.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>627171.1</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>535897.1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>405955.2</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>281638</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>249045.8</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>247508.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>4894450.4</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>3474169.2</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3115077.7</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>2281453.7</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1755034.4</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>1892202.4</v>
+      </c>
+    </row>
+    <row r="34" ht="260" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited's own Statement of Financial Position (Bank column), converted from USD to £ per the FX conversion note on the Cash Flow Statement sheet:
+FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, p.21 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+FY2022 &amp; FY2021: Report and Statutory Accounts 2022, p.17 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
+FY2020: Report and Statutory Accounts 2021, p.15 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
+FY2019: Report and Statutory Accounts 2019, p.12 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2019-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+PRESENTATION NOTE: The Bank column (entity-level) is used throughout for consistency with the Cash Flow Statement sheet - Bank and Group are identical for FY2020-FY2023 (no subsidiary existed) and differ only immaterially for FY2024 (following the Access Bank Malta investment - see Investment in Subsidiary note). The Balance Sheet's line-item structure changed between report vintages: FY2024/FY2023 (AR2024) present 'Money market placements', 'Investment in subsidiary', 'Deferred tax liability' and a 'Prepaid corporation tax' asset as separate lines not present in earlier years; FY2022 (AR2022)/FY2021/FY2020 group these differently (e.g. a single 'Cash at bank' line, no separate money-market-placements or investment-securities split visible pre-FY2021 in the same granularity). Each year's own as-reported labels/granularity are preserved rather than forced into a common shape - blank cells indicate that year's report did not disclose that specific line. The P&amp;L's structure also changed: FY2024/FY2023 use a 'Total operating income' / 'Net operating income' (after ECL) structure; FY2022/FY2021/FY2020 use a similar shape but without the 'Total operating income' subtotal line (ECL is deducted one step later, after 'Other income', directly into 'Net operating income').</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A34:G34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Statement of Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, converted from USD, Bank basis - see source note at bottom for FX methodology and rates used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>283516.2</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>220405.3</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>105009.8</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>73510.8</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>76400.89999999999</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>70388.89999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-120537.4</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-80724.7</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-24532.6</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-12787.8</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-19140.9</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>-21853.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>162978.8</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>139680.5</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>80477.2</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>60723</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>57260</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>48535.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>25613.9</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>24611.7</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>24246.4</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>19737.6</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>20833.1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>17443.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission expense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-2262.2</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-1448.9</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-1614.3</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-1345.9</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-951.2</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-185.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee and commission income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>23351.7</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>23162.8</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>22632.1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>18391.7</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>19881.9</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>17258.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>4834.3</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4056.8</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>3251.4</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1726.2</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1406.7</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1124.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n">
+        <v>5869.8</v>
+      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>191164.7</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>166900.1</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n">
+        <v>66715.39999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Expected credit loss (ECL) allowance / Provision for expected credit losses</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-8476.6</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-6616.1</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-30149.9</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-23609.8</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-45677.9</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-202.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>182688.1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>160284.1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>76210.8</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>63100.8</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>32870.6</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>66715.39999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Personnel expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-30320.3</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-25622.8</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-18183.2</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-16270.7</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-13286.2</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-15289.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-3258.1</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-2057.3</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-1850.7</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-1387.3</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-1798.7</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-1380.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-13459</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-10785.5</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-8692.6</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-7732.1</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-4676.3</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-5280.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-47037.5</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-38465.6</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-28726.6</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-25390.1</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-19761.1</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-21951.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Profit before tax expense</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>135650.6</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>121818.5</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>47484.2</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>37710.8</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>13109.5</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>44764</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Tax expense / Taxation</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>-35723.5</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-31596.5</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-10815.2</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>-8263.799999999999</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-2589.1</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-10069.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Profit after tax expense for the year</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>99927.10000000001</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>90221.89999999999</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>36669.1</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>29447</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>10520.4</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>34694.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(expense)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income on investment securities / net profit on FVOCI securities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>-1032.8</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>1156.4</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-188.5</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>171.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>98894.39999999999</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>91378.3</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>36629.5</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>29509.4</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>10331.9</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>34866.2</v>
+      </c>
+    </row>
+    <row r="28" ht="260" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited's own Statement of Comprehensive Income (Bank column), converted from USD to £ per the FX conversion note on the Cash Flow Statement sheet:
+FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, p.20 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+FY2022 &amp; FY2021: Report and Statutory Accounts 2022, p.16 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
+FY2020: Report and Statutory Accounts 2021, p.14 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
+FY2019: Report and Statutory Accounts 2019, p.11 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2019-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+PRESENTATION NOTE: The Bank column (entity-level) is used throughout for consistency with the Cash Flow Statement sheet - Bank and Group are identical for FY2020-FY2023 (no subsidiary existed) and differ only immaterially for FY2024 (following the Access Bank Malta investment - see Investment in Subsidiary note). The Balance Sheet's line-item structure changed between report vintages: FY2024/FY2023 (AR2024) present 'Money market placements', 'Investment in subsidiary', 'Deferred tax liability' and a 'Prepaid corporation tax' asset as separate lines not present in earlier years; FY2022 (AR2022)/FY2021/FY2020 group these differently (e.g. a single 'Cash at bank' line, no separate money-market-placements or investment-securities split visible pre-FY2021 in the same granularity). Each year's own as-reported labels/granularity are preserved rather than forced into a common shape - blank cells indicate that year's report did not disclose that specific line. The P&amp;L's structure also changed: FY2024/FY2023 use a 'Total operating income' / 'Net operating income' (after ECL) structure; FY2022/FY2021/FY2020 use a similar shape but without the 'Total operating income' subtotal line (ECL is deducted one step later, after 'Other income', directly into 'Net operating income').</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A28:G28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2968,2442 +5703,53 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — Tier 1 Ratio</t>
+          <t>The Access Bank UK Limited — Statement of Changes in Equity</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000, converted from USD, Bank basis - chronological, oldest to newest. See source note for FX methodology/caveat.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Movement</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>Retained earnings</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>Other reserves</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>Currency translation reserve</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>21.88%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Total Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000 (conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>531687.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>402448.5</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>279437.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>248093.1</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Equal to CET1/Tier 1 capital in every year - the Bank holds no AT1 or Tier 2 instruments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="130" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Total Capital Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>21.88%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Total RWAs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000 (conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>2375798.8</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>2033020.6</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1277097.8</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1348332.5</v>
-      </c>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — RWA Breakdown (UK OV1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000, converted from USD - see source note for FX methodology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020 (£'000, conv. from USD)</t>
+          <t>Total equity</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Risk-weighted exposure amounts (RWEAs)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Credit risk (excluding CCR)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n">
-        <v>2145347.2</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1850231.5</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>1139061.5</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>1223557.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Counterparty credit risk (CCR)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n">
-        <v>7696.4</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>5454.2</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>619.8</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>6992.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Of which: credit valuation adjustment (CVA)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n">
-        <v>1727.1</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>684.5</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>147.9</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>2567.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Operational risk (basic indicator approach)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n">
-        <v>221028.9</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>177334.9</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>137268.7</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>115215.6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n">
-        <v>2375798.8</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>2033020.6</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1277097.8</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>1348332.5</v>
-      </c>
-    </row>
-    <row r="11" ht="170" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited's own OV1 (Overview of risk weighted exposure amounts) table, converted from USD to £ at that year's BoE spot rate:
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 4.3, OV1) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 &amp; FY2020: Pillar 3 Disclosures 2022, p.15 (Section 4.3, OV1) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
-FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
-No FY2024 Pillar 3 Disclosures document has been found (same gap already noted on the Pillar 3 metric sheets) - FY2024 cells are blank rather than guessed. The Bank has no market risk RWA requirement in any year shown (its own Pillar 3 reports state market risk is below the CRR de minimis threshold - it holds no trading book) - not a missing-disclosure gap, a genuine nil. 'Of which: credit valuation adjustment (CVA)' is a memo sub-item already included WITHIN 'Counterparty credit risk (CCR)' above it (per the OV1 template's own structure), not an additional component - it will appear to double-count against the Total row in a naive DATA-sum reconciliation check; this is expected and matches the Bank's own table structure.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Leverage Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000 / % (conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total exposure measure</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>3335479.9</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>3357849.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>2499781.8</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1899792.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio (%)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>15.9%</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>12.0%</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>11.18%</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>13.07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2020/FY2021 source tables (UK LR2, in the FY2021 Pillar 3 report) label this 'including claims on central banks'; FY2022 onward (UK KM1 template) labels it 'excluding claims on central banks'. Despite the differing labels, the FY2021 figure is identical (3,379,955) in both the FY2021 report's own table and the FY2022 report's comparative column, so this appears to be inconsistent wording by the Bank rather than a genuine methodology change - shown here as a single continuous row, flagged for visibility.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="130" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000 / % (conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total high-quality liquid assets (HQLA), weighted value</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>708481</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>870655.5</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>596938.8</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows, adjusted value</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n">
-        <v>193806.2</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>193268.6</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>161053.2</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>365.6%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>450.5%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>370.6%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021's $ breakdown (HQLA/net cash outflows) is sourced from the FY2022 Pillar 3 report's comparative column - the FY2021 Pillar 3 report itself only states a single narrative LCR percentage (343.9%, a slightly different figure from the 370.6% shown here), not a KM1-style table with a $ breakdown. The two FY2021 percentages differ slightly, most likely because the narrative figure is a different point-in-time/averaging convention than the KM1 template's 'average of preceding twelve months' basis used here - both are the Bank's own disclosures, this workbook uses the KM1-consistent figure. FY2020 not found in any source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="130" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — NSFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000 / % (conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total available stable funding</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>1475757.9</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1213379.4</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1318835.1</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total required stable funding</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n">
-        <v>875261.5</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>820509.2</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>670287.7</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Net Stable Funding Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>168.6%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>147.9%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>196.8%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021's $ breakdown is sourced from the FY2022 Pillar 3 report's comparative column (the FY2021 report itself does not tabulate NSFR). FY2020 not found in any source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="130" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No MREL disclosure (numeric or qualitative) or UK KM2 template found in any year's Pillar 3 report - not explicitly stated as an exemption, but consistent with the Bank's small size relative to typical MREL-in-scope thresholds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Statement of Financial Position</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000, converted from USD, Bank basis - see source note at bottom for FX methodology and rates used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents / Cash at bank</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>241803</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>364263.6</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>524595.1</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>392792.6</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>117322.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Money market placements</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>10589.3</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>5622.5</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>2976.3</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>2905.5</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>4766.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Investment securities</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>1833749.1</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>803837.1</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>590237.8</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>451184.6</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>261076.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Investment in subsidiary</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>17757.9</v>
-      </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1418050.3</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>1080914.2</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>1049435.4</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>628250.8</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>690790.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Loans and advances to customers</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>1334233.8</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>1196311.6</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>921615.8</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>779823.3</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>651852.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>1623.8</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>894.2</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>904.7</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>698.3</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Right-of-use assets</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>5831.2</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>1938.3</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>3167.7</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>3839.4</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>3551.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Intangible assets</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>6868.6</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>3658.5</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>3183.7</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1980.6</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>1739.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Other financial/non-financial assets</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>20753.2</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>15213.9</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>18961.2</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>19978.7</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>23030.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Prepaid corporation tax</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>146.7</v>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Derivative financial instruments</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>2801.5</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>1368.6</v>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>4894450.4</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>3474169.2</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>3115077.7</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>2281453.7</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>1755034.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Deposits from banks</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>2972616.3</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>1771700.8</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>1654616.8</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>1288483.6</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>842073</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Deposits from customers</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>1238476.6</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>1140155.1</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>1035143.9</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>692107.4</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>641605.3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Lease liabilities</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>5807.9</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>1723.2</v>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Other financial/non-financial liabilities</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>40611.2</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>22374.6</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>18961.6</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>18847.6</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>22021.1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Deferred tax liability</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>1780.7</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>944.5</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>400.2</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>377.1</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>289.2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Derivative financial instruments</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>7986.6</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>1373.8</v>
-      </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>4267279.3</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>2938272.1</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2709122.4</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>1999815.7</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>1505988.6</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>297547.1</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>292475.8</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>225163.5</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>153376.4</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>151804.6</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>333698.6</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>246389.6</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>185105.1</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>132084.4</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>101087.6</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Other reserves</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>-68.59999999999999</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>969.4</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>-168.8</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>-114.8</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>-176.4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Currency translation reserve</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>-4006</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>-3937.8</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>-4144.5</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>-3708</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>-3670</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>627171.1</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>535897.1</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>405955.2</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>281638</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>249045.8</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities and equity</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>4894450.4</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>3474169.2</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>3115077.7</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>2281453.7</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>1755034.4</v>
-      </c>
-    </row>
-    <row r="34" ht="260" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited's own Statement of Financial Position (Bank column), converted from USD to £ per the FX conversion note on the Cash Flow Statement sheet:
-FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, p.21 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-FY2022 &amp; FY2021: Report and Statutory Accounts 2022, p.17 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
-FY2020: Report and Statutory Accounts 2021, p.15 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
-ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
-FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
-PRESENTATION NOTE: The Bank column (entity-level) is used throughout for consistency with the Cash Flow Statement sheet - Bank and Group are identical for FY2020-FY2023 (no subsidiary existed) and differ only immaterially for FY2024 (following the Access Bank Malta investment - see Investment in Subsidiary note). The Balance Sheet's line-item structure changed between report vintages: FY2024/FY2023 (AR2024) present 'Money market placements', 'Investment in subsidiary', 'Deferred tax liability' and a 'Prepaid corporation tax' asset as separate lines not present in earlier years; FY2022 (AR2022)/FY2021/FY2020 group these differently (e.g. a single 'Cash at bank' line, no separate money-market-placements or investment-securities split visible pre-FY2021 in the same granularity). Each year's own as-reported labels/granularity are preserved rather than forced into a common shape - blank cells indicate that year's report did not disclose that specific line. The P&amp;L's structure also changed: FY2024/FY2023 use a 'Total operating income' / 'Net operating income' (after ECL) structure; FY2022/FY2021/FY2020 use a similar shape but without the 'Total operating income' subtotal line (ECL is deducted one step later, after 'Other income', directly into 'Net operating income').</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A34:F34"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="76" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Statement of Comprehensive Income</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000, converted from USD, Bank basis - see source note at bottom for FX methodology and rates used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020 (£'000, conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Operating income</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>283516.2</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>220405.3</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>105009.8</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>73510.8</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>76400.89999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>-120537.4</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>-80724.7</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>-24532.6</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>-12787.8</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>-19140.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Net interest income</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>162978.8</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>139680.5</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>80477.2</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>60723</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>57260</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Fee and commission income</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>25613.9</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>24611.7</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>24246.4</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>19737.6</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>20833.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Fee and commission expense</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>-2262.2</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>-1448.9</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>-1614.3</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>-1345.9</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>-951.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Net fee and commission income</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>23351.7</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>23162.8</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>22632.1</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>18391.7</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>19881.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>4834.3</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>4056.8</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>3251.4</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>1726.2</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>1406.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Other operating income</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n">
-        <v>5869.8</v>
-      </c>
-      <c r="F12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Total operating income</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>191164.7</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>166900.1</v>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Expected credit loss (ECL) allowance / Provision for expected credit losses</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>-8476.6</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>-6616.1</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>-30149.9</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-23609.8</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>-45677.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Net operating income</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>182688.1</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>160284.1</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>76210.8</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>63100.8</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>32870.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Personnel expenses</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>-30320.3</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>-25622.8</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>-18183.2</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-16270.7</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>-13286.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>-3258.1</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>-2057.3</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>-1850.7</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>-1387.3</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>-1798.7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>-13459</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>-10785.5</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>-8692.6</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>-7732.1</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>-4676.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>-47037.5</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>-38465.6</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>-28726.6</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>-25390.1</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>-19761.1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Profit before tax expense</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>135650.6</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>121818.5</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>47484.2</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>37710.8</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>13109.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Tax expense / Taxation</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>-35723.5</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>-31596.5</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>-10815.2</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>-8263.799999999999</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>-2589.1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Profit after tax expense for the year</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>99927.10000000001</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>90221.89999999999</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>36669.1</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>29447</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>10520.4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Other comprehensive income/(expense)</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Other comprehensive income on investment securities / net profit on FVOCI securities</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>-1032.8</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>1156.4</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>-39.6</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>-188.5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Total comprehensive income for the year, net of tax</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>98894.39999999999</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>91378.3</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>36629.5</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>29509.4</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>10331.9</v>
-      </c>
-    </row>
-    <row r="28" ht="260" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited's own Statement of Comprehensive Income (Bank column), converted from USD to £ per the FX conversion note on the Cash Flow Statement sheet:
-FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, p.20 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-FY2022 &amp; FY2021: Report and Statutory Accounts 2022, p.16 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
-FY2020: Report and Statutory Accounts 2021, p.14 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
-ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
-FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
-PRESENTATION NOTE: The Bank column (entity-level) is used throughout for consistency with the Cash Flow Statement sheet - Bank and Group are identical for FY2020-FY2023 (no subsidiary existed) and differ only immaterially for FY2024 (following the Access Bank Malta investment - see Investment in Subsidiary note). The Balance Sheet's line-item structure changed between report vintages: FY2024/FY2023 (AR2024) present 'Money market placements', 'Investment in subsidiary', 'Deferred tax liability' and a 'Prepaid corporation tax' asset as separate lines not present in earlier years; FY2022 (AR2022)/FY2021/FY2020 group these differently (e.g. a single 'Cash at bank' line, no separate money-market-placements or investment-securities split visible pre-FY2021 in the same granularity). Each year's own as-reported labels/granularity are preserved rather than forced into a common shape - blank cells indicate that year's report did not disclose that specific line. The P&amp;L's structure also changed: FY2024/FY2023 use a 'Total operating income' / 'Net operating income' (after ECL) structure; FY2022/FY2021/FY2020 use a similar shape but without the 'Total operating income' subtotal line (ECL is deducted one step later, after 'Other income', directly into 'Net operating income').</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A28:F28"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Statement of Changes in Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000, converted from USD, Bank basis - chronological, oldest to newest. See source note for FX methodology/caveat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Other reserves</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Currency translation reserve</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 1 January 2020</t>
+          <t>Balance as at 1 January 2019</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -5415,14 +5761,14 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax for the year (2020)</t>
+          <t>Profit after tax for the year (2019)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>10520.4</v>
+        <v>34694.4</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -5431,13 +5777,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>10520.4</v>
+        <v>34694.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive expense for the year (2020)</t>
+          <t>Other comprehensive income for the year (2019)</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
@@ -5447,70 +5793,70 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>-188.5</v>
+        <v>171.8</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-188.5</v>
+        <v>171.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Total comprehensive income for the year (2020)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Translation impact on SOCI (2019)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>10520.4</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>-188.5</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>10331.9</v>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-940.7</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-940.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Balance as at 31 December 2020</t>
+          <t>Total comprehensive income for the year (2019)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>151804.6</v>
+        <v>0</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>101087.6</v>
+        <v>34694.4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-176.4</v>
+        <v>171.8</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-3670</v>
+        <v>-940.7</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>249045.8</v>
+        <v>33925.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax for the year (2021)</t>
+          <t>Proceeds from shares issued (2019)</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
+        <v>26239.7</v>
+      </c>
+      <c r="C9" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>29447</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -5519,86 +5865,86 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>29447</v>
+        <v>26239.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income for the year (2021)</t>
+          <t>Translation impact on share capital (2019)</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0</v>
+        <v>-2172.6</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>62.3</v>
+        <v>0</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>62.3</v>
+        <v>-2172.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year (2021)</t>
+          <t>Balance as at 31 December 2019</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0</v>
+        <v>156987.3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>29447</v>
+        <v>94315.5</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>62.3</v>
+        <v>0.7</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>-3795.3</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>29509.4</v>
+        <v>247508.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Balance as at 31 December 2021</t>
+          <t>Balance as at 1 January 2020</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>153376.4</v>
+        <v>156987.3</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>132084.4</v>
+        <v>94315.5</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-114.8</v>
+        <v>0.7</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-3708</v>
+        <v>-3795.3</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>281638</v>
+        <v>247508.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax for the year (2022)</t>
+          <t>Profit after tax for the year (2020)</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>36669.1</v>
+        <v>10520.4</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>0</v>
@@ -5607,13 +5953,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>36669.1</v>
+        <v>10520.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive expense for the year (2022)</t>
+          <t>Other comprehensive expense for the year (2020)</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
@@ -5623,158 +5969,158 @@
         <v>0</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-39.6</v>
+        <v>-188.5</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-39.6</v>
+        <v>-188.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year (2022)</t>
+          <t>Total comprehensive income for the year (2020)</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>36669.1</v>
+        <v>10520.4</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>-39.6</v>
+        <v>-188.5</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>36629.5</v>
+        <v>10331.9</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Proceeds from shares issued (2022)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>52580.5</v>
-      </c>
-      <c r="C16" s="6" t="n">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2020</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>151804.6</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>101087.6</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-176.4</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3670</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>249045.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax for the year (2021)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="C17" s="6" t="n">
+        <v>29447</v>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>52580.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Balance as at 31 December 2022</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>225163.5</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>185105.1</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>-168.8</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>-4144.5</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>405955.2</v>
+      <c r="F17" s="6" t="n">
+        <v>29447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax for the year (2023)</t>
+          <t>Other comprehensive income for the year (2021)</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>90221.89999999999</v>
+        <v>0</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0</v>
+        <v>62.3</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>90221.89999999999</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Other comprehensive income for the year (2023)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (2021)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="5" t="n">
+        <v>29447</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>1156.4</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>1156.4</v>
+      <c r="F19" s="5" t="n">
+        <v>29509.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year (2023)</t>
+          <t>Balance as at 31 December 2021</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0</v>
+        <v>153376.4</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>90221.89999999999</v>
+        <v>132084.4</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1156.4</v>
+        <v>-114.8</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>-3708</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>91378.3</v>
+        <v>281638</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Proceeds from shares issued (2023)</t>
+          <t>Profit after tax for the year (2022)</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>80392.3</v>
+        <v>0</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0</v>
+        <v>36669.1</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>0</v>
@@ -5783,64 +6129,64 @@
         <v>0</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>80392.3</v>
+        <v>36669.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Dividends declared (2023)</t>
+          <t>Other comprehensive expense for the year (2022)</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>-18044.4</v>
+        <v>0</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0</v>
+        <v>-39.6</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-18044.4</v>
+        <v>-39.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Balance as at 31 December 2023</t>
+          <t>Total comprehensive income for the year (2022)</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>292475.8</v>
+        <v>0</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>246389.6</v>
+        <v>36669.1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>969.4</v>
+        <v>-39.6</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-3937.8</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>535897.1</v>
+        <v>36629.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax for the year (2024)</t>
+          <t>Proceeds from shares issued (2022)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
+        <v>52580.5</v>
+      </c>
+      <c r="C24" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>99927.10000000001</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>0</v>
@@ -5849,114 +6195,291 @@
         <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>99927.10000000001</v>
+        <v>52580.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Other comprehensive expense for the year (2024)</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>225163.5</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>185105.1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-168.8</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-4144.5</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>405955.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax for the year (2023)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C26" s="6" t="n">
+        <v>90221.89999999999</v>
+      </c>
+      <c r="D26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="6" t="n">
-        <v>-1032.8</v>
-      </c>
-      <c r="E25" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>-1032.8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Total comprehensive income for the year (2024)</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>99927.10000000001</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>-1032.8</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>98894.39999999999</v>
+      <c r="F26" s="6" t="n">
+        <v>90221.89999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Dividends declared (2024)</t>
+          <t>Other comprehensive income for the year (2023)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>-18624.9</v>
+        <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0</v>
+        <v>1156.4</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-18624.9</v>
+        <v>1156.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>Total comprehensive income for the year (2023)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>90221.89999999999</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1156.4</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>91378.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Proceeds from shares issued (2023)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>80392.3</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>80392.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Dividends declared (2023)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-18044.4</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-18044.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>292475.8</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>246389.6</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>969.4</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>-3937.8</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>535897.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax for the year (2024)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>99927.10000000001</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>99927.10000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive expense for the year (2024)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-1032.8</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-1032.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (2024)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>99927.10000000001</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>-1032.8</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>98894.39999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Dividends declared (2024)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>-18624.9</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>-18624.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>Balance as at 31 December 2024</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B36" s="5" t="n">
         <v>297547.1</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C36" s="5" t="n">
         <v>333698.6</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D36" s="5" t="n">
         <v>-68.59999999999999</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E36" s="5" t="n">
         <v>-4006</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F36" s="5" t="n">
         <v>627171.1</v>
       </c>
     </row>
-    <row r="30" ht="280" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="38" ht="280" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited's own Statement of Changes in Equity (Bank basis), converted from USD to £ (Balance rows at that date's BoE spot rate; movement rows at that calendar year's BoE average rate - same FX methodology as the Cash Flow Statement sheet):
 2024 &amp; 2023 movements: Report &amp; Financial Statements 2024, p.22 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
 2022 &amp; 2021 movements: Report and Statutory Accounts 2022, p.18 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
 2020 movements: Report and Statutory Accounts 2021, p.16 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
-ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
-FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+2019 movements: Report and Statutory Accounts 2019, p.13 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2019-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
 EQUITY SHEET FX CAVEAT: because this roll-forward mixes point-in-time Balance rows (spot rate) with in-year movement rows (average rate) - the same two-rate approach used for the Cash Flow Statement - each period's £ closing balance will differ very slightly from £ opening balance + £ movements (unlike the Cash Flow Statement, this sheet has no natural 'FX translation' line to absorb the difference, so no plug row is shown here). The underlying USD figures (see rows above) tie out exactly in every period; this is purely a £ presentation artefact of using two different conversion rates, not a data quality issue.
-PRESENTATION NOTE: The Balance as at 1 January 2020 row is left blank (not converted) since it would require a 31 December 2019 GBP/USD spot rate, which hasn't been sourced for this project - matching the same gap already noted for the Cash Flow Statement's FY2020 opening balance. FY2022's own statement labels its 'Proceeds from shares issued' row as part of a combined 'Total comprehensive income for the year' total (which would overstate that label); this workbook instead reports 'Total comprehensive income for the year (2022)' as profit + OCI only (excluding the share issuance), with 'Proceeds from shares issued' shown as its own separate row immediately after - the Balance at 31 December 2022 row still ties to the sum of all rows in between, this is a relabeling for clarity only, not a change to any figure.</t>
+PRESENTATION NOTE: FY2022's own statement labels its 'Proceeds from shares issued' row as part of a combined 'Total comprehensive income for the year' total (which would overstate that label); this workbook instead reports 'Total comprehensive income for the year (2022)' as profit + OCI only (excluding the share issuance), with 'Proceeds from shares issued' shown as its own separate row immediately after - the Balance at 31 December 2022 row still ties to the sum of all rows in between, this is a relabeling for clarity only, not a change to any figure.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A38:F38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5968,7 +6491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -5977,6 +6500,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6022,6 +6546,11 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2020 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000, conv. from USD)</t>
         </is>
       </c>
     </row>
@@ -6036,6 +6565,7 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6058,6 +6588,9 @@
       <c r="F5" s="6" t="n">
         <v>13109.5</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>44764</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6080,6 +6613,9 @@
       <c r="F6" s="6" t="n">
         <v>1357.6</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>238.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6102,6 +6638,9 @@
       <c r="F7" s="6" t="n">
         <v>441</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>359.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -6124,6 +6663,9 @@
       <c r="F8" s="6" t="n">
         <v>45677.9</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>221.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -6144,6 +6686,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -6158,6 +6701,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -6180,6 +6724,9 @@
       <c r="F11" s="6" t="n">
         <v>13034.2</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>142015.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6202,6 +6749,9 @@
       <c r="F12" s="6" t="n">
         <v>-268309.5</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>-333508.6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -6224,6 +6774,9 @@
       <c r="F13" s="6" t="n">
         <v>-9491.799999999999</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>-448.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -6246,6 +6799,9 @@
       <c r="F14" s="6" t="n">
         <v>-161451.2</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>-152736.7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -6268,6 +6824,9 @@
       <c r="F15" s="6" t="n">
         <v>74423.3</v>
       </c>
+      <c r="G15" s="6" t="n">
+        <v>128718.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -6290,6 +6849,9 @@
       <c r="F16" s="6" t="n">
         <v>-232</v>
       </c>
+      <c r="G16" s="6" t="n">
+        <v>5562.1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -6312,6 +6874,9 @@
       <c r="F17" s="6" t="n">
         <v>-16485.6</v>
       </c>
+      <c r="G17" s="6" t="n">
+        <v>-8622.9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -6333,6 +6898,9 @@
       </c>
       <c r="F18" s="5" t="n">
         <v>-307926.5</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-173436.3</v>
       </c>
     </row>
     <row r="19">
@@ -6346,6 +6914,7 @@
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -6367,6 +6936,9 @@
       </c>
       <c r="F20" s="6" t="n">
         <v>46913.9</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-16353.4</v>
       </c>
     </row>
     <row r="21">
@@ -6382,6 +6954,7 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -6404,6 +6977,9 @@
       <c r="F22" s="6" t="n">
         <v>-579.3</v>
       </c>
+      <c r="G22" s="6" t="n">
+        <v>-313.9</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -6426,6 +7002,9 @@
       <c r="F23" s="6" t="n">
         <v>-291.3</v>
       </c>
+      <c r="G23" s="6" t="n">
+        <v>-613</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -6447,6 +7026,9 @@
       </c>
       <c r="F24" s="5" t="n">
         <v>46043.3</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-17280.2</v>
       </c>
     </row>
     <row r="25">
@@ -6460,6 +7042,7 @@
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -6476,6 +7059,9 @@
       </c>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n">
+        <v>26239.7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -6494,6 +7080,7 @@
       <c r="F27" s="6" t="n">
         <v>-1036.9</v>
       </c>
+      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -6510,6 +7097,7 @@
       <c r="D28" s="6" t="n"/>
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -6526,6 +7114,7 @@
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="n"/>
       <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -6542,6 +7131,7 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -6564,6 +7154,9 @@
       <c r="F31" s="5" t="n">
         <v>-1036.9</v>
       </c>
+      <c r="G31" s="5" t="n">
+        <v>26239.7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -6586,6 +7179,9 @@
       <c r="F32" s="5" t="n">
         <v>-262920.2</v>
       </c>
+      <c r="G32" s="5" t="n">
+        <v>-164476.8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -6605,7 +7201,10 @@
       <c r="E33" s="6" t="n">
         <v>117322.9</v>
       </c>
-      <c r="F33" s="6" t="n"/>
+      <c r="F33" s="6" t="n">
+        <v>376653.1</v>
+      </c>
+      <c r="G33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -6628,6 +7227,9 @@
       <c r="F34" s="6" t="n">
         <v>176.5</v>
       </c>
+      <c r="G34" s="6" t="n">
+        <v>-2767.5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -6647,7 +7249,10 @@
       <c r="E35" s="6" t="n">
         <v>5821.6</v>
       </c>
-      <c r="F35" s="6" t="n"/>
+      <c r="F35" s="6" t="n">
+        <v>3413.5</v>
+      </c>
+      <c r="G35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -6669,6 +7274,9 @@
       </c>
       <c r="F36" s="5" t="n">
         <v>117322.9</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>376653.1</v>
       </c>
     </row>
     <row r="38" ht="340" customHeight="1">
@@ -6679,16 +7287,17 @@
 FY2023: Report and Financial Statements 2023, p.21 (Statement of Cash Flows) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/07/ACCESS_BANK_AR_2023_Financial-statements.pdf
 FY2022: Report and Statutory Accounts 2022, p.19 (Statement of Cash Flows) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
 FY2021 &amp; FY2020: Report and Statutory Accounts 2021, p.17 (Statement of Cash Flows) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
+FY2019: Report and Statutory Accounts 2019, p.14 (Statement of Cash Flows) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
 Activity-total rows may be off by up to £0.1k from summing the visible line items above them, since each £ line is independently rounded to 1 decimal place before summing; the full statement ties exactly end-to-end via the net change, opening balance, exchange-rate-effect and translation-effect lines (verified to the penny in £'000 terms for FY2021-FY2024; FY2020 has no opening balance, see FX note).
-ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
-FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2019-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
 PRESENTATION NOTE: presentation differs slightly between report vintages, each year's own as-reported line items/labels are preserved rather than forced into a common shape. FY2023/FY2024 split lease payments into separate 'Lease payments principal' and 'Lease payments interest' rows; FY2020-FY2022 instead show a single combined 'Lease payments' row (FY2022's own report keeps the combined presentation even though FY2023's report restates FY2022 as a split comparative - FY2022's own report's combined figure is used here, per this project's convention of preferring each year's own report). A handful of line items differ by $1-$3 between a year's own primary statement and its appearance as the following year's comparative column (immaterial rounding, e.g. FY2021 'Operating cash flows before movements in working capital' is $86,336,098 in AR2021's own statement vs $86,336,099 in AR2022's comparative) - each year's own primary statement figure is used throughout.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6700,7 +7309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -6709,6 +7318,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6754,6 +7364,11 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2020 (£'000, conv. from USD)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000, conv. from USD)</t>
         </is>
       </c>
     </row>
@@ -6768,6 +7383,7 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6784,6 +7400,7 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6800,6 +7417,7 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6816,6 +7434,7 @@
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -6834,6 +7453,9 @@
       <c r="F8" s="6" t="n">
         <v>80363.3</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>83790.10000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -6852,11 +7474,14 @@
       <c r="F9" s="6" t="n">
         <v>571489.5</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>577895.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Total loans and advances to customers (gross FY2023-24 / net FY2020-22)</t>
+          <t>Total loans and advances to customers (gross FY2023-24 / net FY2019-22)</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -6873,6 +7498,9 @@
       </c>
       <c r="F10" s="5" t="n">
         <v>651852.8</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>661685.5</v>
       </c>
     </row>
     <row r="11">
@@ -6886,6 +7514,7 @@
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6908,6 +7537,9 @@
       <c r="F12" s="6" t="n">
         <v>540993.2</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>621201.2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -6930,6 +7562,9 @@
       <c r="F13" s="6" t="n">
         <v>70874.5</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>28789.3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -6952,6 +7587,9 @@
       <c r="F14" s="6" t="n">
         <v>82761</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>12113</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -6973,6 +7611,9 @@
       </c>
       <c r="F15" s="5" t="n">
         <v>694628.7</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>662103.5</v>
       </c>
     </row>
     <row r="16">
@@ -6986,6 +7627,7 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7008,6 +7650,9 @@
       <c r="F17" s="6" t="n">
         <v>-539.2</v>
       </c>
+      <c r="G17" s="6" t="n">
+        <v>-114.4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7030,6 +7675,9 @@
       <c r="F18" s="6" t="n">
         <v>-6385.2</v>
       </c>
+      <c r="G18" s="6" t="n">
+        <v>-303.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7052,6 +7700,9 @@
       <c r="F19" s="6" t="n">
         <v>-35851.5</v>
       </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -7073,6 +7724,9 @@
       </c>
       <c r="F20" s="5" t="n">
         <v>-42775.8</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-417.9</v>
       </c>
     </row>
     <row r="21">
@@ -7086,6 +7740,7 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -7118,6 +7773,11 @@
           <t>6.2%</t>
         </is>
       </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -7150,6 +7810,11 @@
           <t>11.9%</t>
         </is>
       </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -7180,6 +7845,11 @@
       <c r="F24" s="6" t="inlineStr">
         <is>
           <t>43.3%</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7190,15 +7860,16 @@
 FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, p.51-52 (Note 27d, Loans to customers ECL staging table) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
 FY2022 &amp; FY2021: Report and Statutory Accounts 2022, p.43 (Note 24d) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
 FY2020: Report and Statutory Accounts 2021, p.42 (Note 24d, comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
-ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2020-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
-FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2020 average is newly sourced for this workbook (no earlier bank in this series needed a full FY2020 column). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. FY2020's opening cash balance is left blank (not converted) since it would require a 31 December 2019 spot rate, which hasn't been sourced for this project - FY2020's closing balance and flow lines ARE populated, just not its opening balance or a translation plug. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+FY2019: Report and Statutory Accounts 2019, p.37 (Note 23d) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
+ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2019-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
 PRESENTATION NOTE: the loan-book-by-product split is NOT presented on a consistent basis across all 5 years - FY2024/FY2023 disclose a GROSS product split (Loans to corporates / secured on property / other secured personal loans, from Note 18/17); FY2022/FY2021/FY2020 only disclose a NET-of-allowance Retail/Corporate split (from the credit risk exposure table), not a gross one at that granularity - each row is labelled to make this explicit, and the 'Total loans and advances to customers' row for each year sums exactly to whichever rows are populated for that year (gross FY2023-24, net FY2020-22) - do not compare that total row directly across the gross/net boundary. The by-IFRS-9-stage breakdown below IS on a consistent gross basis for all 5 years and ties to each year's own Balance Sheet 'Loans and advances to customers' gross figure. FY2024's Stage 3 loss allowance coverage (0.3%) is much lower than FY2023's (28.7%) - both figures are as directly reported; the Bank's own notes attribute this to a large trade-finance Stage 3 exposure ($49.9m) that is substantially collateralised by credit insurance, so most of its gross balance is not provisioned for - flagged here for visibility rather than smoothed over.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A26:G26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7210,7 +7881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7219,6 +7890,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7266,6 +7938,11 @@
           <t>FY2020</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7286,6 +7963,7 @@
       <c r="F4" s="6" t="n">
         <v>248093.1</v>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -7294,13 +7972,14 @@
 FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7312,7 +7991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7321,6 +8000,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7368,6 +8048,11 @@
           <t>FY2020</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7375,7 +8060,11 @@
           <t>Common Equity Tier 1 (CET1) ratio</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>22.4%</t>
@@ -7396,6 +8085,7 @@
           <t>18.40%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="6" ht="130" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -7404,13 +8094,14 @@
 FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7422,7 +8113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7431,6 +8122,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7478,6 +8170,11 @@
           <t>FY2020</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7498,6 +8195,7 @@
       <c r="F4" s="6" t="n">
         <v>248093.1</v>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -7513,14 +8211,15 @@
 FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025) - FY2024 cells are blank rather than guessed. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/ACCESS BANK UK FINANCIALS.xlsx
+++ b/banks/ACCESS BANK UK FINANCIALS.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -197,13 +197,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -240,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -264,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -288,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -312,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -355,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -395,13 +395,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -438,7 +438,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -462,7 +462,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -486,7 +486,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -529,8 +529,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,13 +569,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -612,7 +612,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -636,7 +636,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -660,7 +660,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -684,7 +684,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -727,8 +727,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -767,13 +767,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -810,7 +810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -834,7 +834,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -858,7 +858,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -882,7 +882,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -925,8 +925,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -965,13 +965,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1007,14 +1007,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1040,14 +1040,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1073,14 +1073,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1106,14 +1106,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1139,14 +1139,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1172,14 +1172,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1223,8 +1223,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1263,7 +1263,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1278,9 +1278,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1300,9 +1300,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1322,9 +1322,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1344,9 +1344,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1366,9 +1366,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4339,7 +4339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4468,38 +4468,32 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Investment securities</t>
+          <t>Investment securities - US Treasury bills and government bonds, at FVPL</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1833749.1</v>
+        <v>1575247.7</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>803837.1</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>590237.8</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>451184.6</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>261076.9</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>315762.7</v>
-      </c>
+        <v>800099</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Investment in subsidiary</t>
+          <t>Investment securities - US Treasury bills, at FVOCI</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>17757.9</v>
-      </c>
-      <c r="C8" s="6" t="n"/>
+        <v>255229</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -4508,553 +4502,644 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1418050.3</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>1080914.2</v>
-      </c>
+          <t>Investment securities - US Treasury bills and government bonds (measurement basis not separately disclosed pre-FY2023)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n">
-        <v>1049435.4</v>
+        <v>588173.4</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>628250.8</v>
+        <v>449301.1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>690790.5</v>
+        <v>259869.2</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>510453.6</v>
+        <v>314245.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Loans and advances to customers</t>
+          <t>Investment securities - Listed equity securities in financial institutions</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1334233.8</v>
+        <v>3272.3</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1196311.6</v>
+        <v>3738.1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>921615.8</v>
+        <v>2064.4</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>779823.3</v>
+        <v>1883.5</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>651852.8</v>
+        <v>1207.7</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>661685.5</v>
+        <v>1517.3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>1623.8</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>894.2</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>904.7</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>698.3</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>904</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>2095.7</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Total investment securities</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1833749.1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>803837.1</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>590237.8</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>451184.6</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>261076.9</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>315762.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Right-of-use assets</t>
+          <t>Investment in subsidiary</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>5831.2</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>1938.3</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>3167.7</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>3839.4</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>3551.3</v>
-      </c>
+        <v>17757.9</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Loans and advances to banks</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>6868.6</v>
+        <v>1418050.3</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3658.5</v>
+        <v>1080914.2</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3183.7</v>
+        <v>1049435.4</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1980.6</v>
+        <v>628250.8</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1739.7</v>
+        <v>690790.5</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1899.7</v>
+        <v>510453.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Other financial/non-financial assets</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>20753.2</v>
+        <v>1334233.8</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>15213.9</v>
+        <v>1196311.6</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>18961.2</v>
+        <v>921615.8</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>19978.7</v>
+        <v>779823.3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>23030.2</v>
+        <v>651852.8</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>6059.5</v>
+        <v>661685.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Prepaid corporation tax</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>388.8</v>
+        <v>1623.8</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>146.7</v>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
+        <v>894.2</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>904.7</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>698.3</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>904</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2095.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Right-of-use assets</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>2801.5</v>
+        <v>5831.2</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1368.6</v>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+        <v>1938.3</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>3167.7</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>3839.4</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>3551.3</v>
+      </c>
       <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>4894450.4</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>3474169.2</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>3115077.7</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>2281453.7</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>1755034.4</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>1892202.4</v>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>6868.6</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>3658.5</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3183.7</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1980.6</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>1739.7</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>1899.7</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Other financial/non-financial assets</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>20753.2</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>15213.9</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>18961.2</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>19978.7</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>23030.2</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>6059.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Deposits from banks</t>
+          <t>Prepaid corporation tax</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>2972616.3</v>
+        <v>388.8</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1771700.8</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>1654616.8</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>1288483.6</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>842073</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>1027714.4</v>
-      </c>
+        <v>146.7</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Deposits from customers</t>
+          <t>Derivative financial instruments</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1238476.6</v>
+        <v>2801.5</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1140155.1</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>1035143.9</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>692107.4</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>641605.3</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>591188.3</v>
-      </c>
+        <v>1368.6</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Lease liabilities</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>5807.9</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>1723.2</v>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>4894450.4</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3474169.2</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3115077.7</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2281453.7</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1755034.4</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1892202.4</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Other financial/non-financial liabilities</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>40611.2</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>22374.6</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>18961.6</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>18847.6</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>22021.1</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>25614.5</v>
-      </c>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Deferred tax liability</t>
+          <t>Deposits from banks</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>1780.7</v>
+        <v>2972616.3</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>944.5</v>
+        <v>1771700.8</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>400.2</v>
+        <v>1654616.8</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>377.1</v>
+        <v>1288483.6</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>289.2</v>
+        <v>842073</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>176.9</v>
+        <v>1027714.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Deposits from customers</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>7986.6</v>
+        <v>1238476.6</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1373.8</v>
-      </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
+        <v>1140155.1</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>1035143.9</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>692107.4</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>641605.3</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>591188.3</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>4267279.3</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>2938272.1</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2709122.4</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>1999815.7</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>1505988.6</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>1644694.2</v>
-      </c>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>5807.9</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>1723.2</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Other financial/non-financial liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>40611.2</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>22374.6</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>18961.6</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>18847.6</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>22021.1</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>25614.5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Deferred tax liability</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>297547.1</v>
+        <v>1780.7</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>292475.8</v>
+        <v>944.5</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>225163.5</v>
+        <v>400.2</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>153376.4</v>
+        <v>377.1</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>151804.6</v>
+        <v>289.2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>156987.3</v>
+        <v>176.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>7986.6</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>1373.8</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4267279.3</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>2938272.1</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2709122.4</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1999815.7</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1505988.6</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1644694.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>297547.1</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>292475.8</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>225163.5</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>153376.4</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>151804.6</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>156987.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>Retained earnings</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B32" s="6" t="n">
         <v>333698.6</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C32" s="6" t="n">
         <v>246389.6</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D32" s="6" t="n">
         <v>185105.1</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E32" s="6" t="n">
         <v>132084.4</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F32" s="6" t="n">
         <v>101087.6</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G32" s="6" t="n">
         <v>94315.5</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Other reserves</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B33" s="6" t="n">
         <v>-68.59999999999999</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C33" s="6" t="n">
         <v>969.4</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D33" s="6" t="n">
         <v>-168.8</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E33" s="6" t="n">
         <v>-114.8</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F33" s="6" t="n">
         <v>-176.4</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G33" s="6" t="n">
         <v>0.7</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B34" s="6" t="n">
         <v>-4006</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C34" s="6" t="n">
         <v>-3937.8</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D34" s="6" t="n">
         <v>-4144.5</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E34" s="6" t="n">
         <v>-3708</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F34" s="6" t="n">
         <v>-3670</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G34" s="6" t="n">
         <v>-3795.3</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B35" s="5" t="n">
         <v>627171.1</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C35" s="5" t="n">
         <v>535897.1</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D35" s="5" t="n">
         <v>405955.2</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E35" s="5" t="n">
         <v>281638</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F35" s="5" t="n">
         <v>249045.8</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="G35" s="5" t="n">
         <v>247508.2</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Total liabilities and equity</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B36" s="5" t="n">
         <v>4894450.4</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C36" s="5" t="n">
         <v>3474169.2</v>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D36" s="5" t="n">
         <v>3115077.7</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E36" s="5" t="n">
         <v>2281453.7</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F36" s="5" t="n">
         <v>1755034.4</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G36" s="5" t="n">
         <v>1892202.4</v>
       </c>
     </row>
-    <row r="34" ht="260" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="38" ht="260" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited's own Statement of Financial Position (Bank column), converted from USD to £ per the FX conversion note on the Cash Flow Statement sheet:
 FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, p.21 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
 FY2022 &amp; FY2021: Report and Statutory Accounts 2022, p.17 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
 FY2020: Report and Statutory Accounts 2021, p.15 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
 FY2019: Report and Statutory Accounts 2019, p.12 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
+Investment securities breakdown (Bank column) - by issuer type in all years, plus measurement basis (FVPL/FVOCI) where the Bank separately discloses it:
+FY2024 &amp; FY2023: Report &amp; Financial Statements 2024, Note 16 'Investment securities', p.36 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+FY2022 &amp; FY2021: Report and Statutory Accounts 2022, Note 13 'Investment securities', p.30 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2023/07/ACCESS_BANK_AR22_Accs.pdf
+FY2020: Report and Statutory Accounts 2021, Note 13 'Investment securities' (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
+FY2019: Report and Statutory Accounts 2019, Note 12 'Investment securities', p.27 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
 ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead reconstructed via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. Companies House filing history confirms the latest filed accounts are 'Group of companies' accounts made up to 31 December 2024' (filed 22 Sep 2025) - no FY2025 Annual Report or Pillar 3 disclosure has been published yet, and no later Pillar 3 edition than the 2023 one has been found (the Bank's Reports page showed only the 2023 edition as of a 16 Nov 2025 Wayback snapshot, the most recent snapshot available). This workbook therefore covers FY2019-FY2024 (shifted one year earlier than most other banks in this series, which run FY2021-FY2025) - 5 years of cash flow, but Pillar 3 metrics only to FY2023 (4 years); FY2024 Pillar 3 cells are blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed.
 FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all three share the same 31 December fiscal year-end; FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
 PRESENTATION NOTE: The Bank column (entity-level) is used throughout for consistency with the Cash Flow Statement sheet - Bank and Group are identical for FY2020-FY2023 (no subsidiary existed) and differ only immaterially for FY2024 (following the Access Bank Malta investment - see Investment in Subsidiary note). The Balance Sheet's line-item structure changed between report vintages: FY2024/FY2023 (AR2024) present 'Money market placements', 'Investment in subsidiary', 'Deferred tax liability' and a 'Prepaid corporation tax' asset as separate lines not present in earlier years; FY2022 (AR2022)/FY2021/FY2020 group these differently (e.g. a single 'Cash at bank' line, no separate money-market-placements or investment-securities split visible pre-FY2021 in the same granularity). Each year's own as-reported labels/granularity are preserved rather than forced into a common shape - blank cells indicate that year's report did not disclose that specific line. The P&amp;L's structure also changed: FY2024/FY2023 use a 'Total operating income' / 'Net operating income' (after ECL) structure; FY2022/FY2021/FY2020 use a similar shape but without the 'Total operating income' subtotal line (ECL is deducted one step later, after 'Other income', directly into 'Net operating income').</t>
@@ -5063,7 +5148,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/ACCESS BANK UK FINANCIALS.xlsx
+++ b/banks/ACCESS BANK UK FINANCIALS.xlsx
@@ -2103,9 +2103,6 @@
       <c r="AY10" t="n">
         <v>365.6</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>176.65</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2989,11 +2986,7 @@
           <t>LCR</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>176.65%</t>
-        </is>
-      </c>
+      <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="inlineStr">
         <is>
           <t>365.6%</t>
@@ -3163,7 +3156,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3246,9 @@
           <t>Total capital</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="n">
+        <v>599900.9</v>
+      </c>
       <c r="C4" s="6" t="n">
         <v>531687.1</v>
       </c>
@@ -3280,7 +3278,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3404,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3517,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3873,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3989,14 +3999,10 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Liquidity Coverage Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>176.65%</t>
-        </is>
-      </c>
+          <t>Liquidity Coverage Ratio (%) (KM1, average of preceding 12 months)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>365.6%</t>
@@ -4015,29 +4021,53 @@
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021's $ breakdown (HQLA/net cash outflows) is sourced from the FY2022 Pillar 3 report's comparative column - the FY2021 Pillar 3 report itself only states a single narrative LCR percentage (343.9%, a slightly different figure from the 370.6% shown here), not a KM1-style table with a $ breakdown. The two FY2021 percentages differ slightly, most likely because the narrative figure is a different point-in-time/averaging convention than the KM1 template's 'average of preceding twelve months' basis used here - both are the Bank's own disclosures, this workbook uses the KM1-consistent figure. FY2020 not found in any source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="130" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio (%) (point-in-time at 31 December)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>176.65%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>275.47%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Note: TWO DIFFERENT BASES, deliberately kept on separate rows. The KM1 row is the Bank's 'average of preceding twelve months' figure and is the basis used for FY2021-FY2023. The point-in-time row is the Bank's year-end spot LCR. They are NOT comparable: for FY2023 the Bank discloses BOTH - 365.6% on the KM1 average basis (Pillar 3 Disclosures 2023, p.6 row 17) and 275.5% at 31 December 2023 (same document, Section 8 narrative), a 90-point gap. FY2024 has no Pillar 3 report, so only the point-in-time figure (176.65%, per the Annual Report 2024 KPI table) exists; it is shown on the point-in-time row and the KM1 average row is left BLANK for FY2024 rather than continued with a different-basis number. An earlier revision of this workbook placed 176.65% directly in the KM1 average row, which made the ratio appear to fall 365.6% -&gt; 176.65%; the like-for-like point-in-time move is 275.47% -&gt; 176.65%. FY2021's $ breakdown (HQLA/net cash outflows) is sourced from the FY2022 Pillar 3 report's comparative column - the FY2021 Pillar 3 report itself only states a single narrative LCR percentage (343.9%), not a KM1-style table with a $ breakdown; that narrative figure is again a different convention from the 370.6% KM1 figure shown here. FY2020 not found in any source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="130" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
 FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4190,7 +4220,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4353,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8071,9 @@
           <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="n">
+        <v>599900.9</v>
+      </c>
       <c r="C4" s="6" t="n">
         <v>531687.1</v>
       </c>
@@ -8058,7 +8096,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8221,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8311,9 @@
           <t>Tier 1 capital</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="n">
+        <v>599900.9</v>
+      </c>
       <c r="C4" s="6" t="n">
         <v>531687.1</v>
       </c>
@@ -8297,7 +8343,10 @@
 FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
 FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-No FY2024 Pillar 3 Disclosures document has been found (the Bank's Reports page showed only the 2023 edition as of the most recent available Wayback Machine snapshot, 16 Nov 2025). However, the FY2024 Annual Report's KPI table provides entity-level Tier 1 capital ratio (20.18%) and point-in-time LCR (176.65%); these are populated where the workbook's metric basis matches. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>

--- a/banks/ACCESS BANK UK FINANCIALS.xlsx
+++ b/banks/ACCESS BANK UK FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3052,6 +3053,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Tier 1 Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 (conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>599900.9</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>531687.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>402448.5</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>279437.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>248093.1</v>
+      </c>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Equal to CET1 capital in every year - the Bank holds no Additional Tier 1 (AT1) instruments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3171,7 +3295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3289,131 +3413,6 @@
   <mergeCells count="2">
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — Total Capital Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.18%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>21.88%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.40%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="n"/>
-    </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
-For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
-NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3440,14 +3439,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — Total RWAs</t>
+          <t>The Access Bank UK Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000 (conv. from USD)</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3491,21 +3490,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n">
-        <v>2375798.8</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>2033020.6</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1277097.8</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1348332.5</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
       </c>
       <c r="G4" s="6" t="n"/>
     </row>
@@ -3533,6 +3544,119 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 (conv. from USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n">
+        <v>2375798.8</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2033020.6</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1277097.8</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1348332.5</v>
+      </c>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
+For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3739,7 +3863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3889,7 +4013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4073,7 +4197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4236,7 +4360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8002,10 +8126,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -8017,21 +8141,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — CET1 Capital</t>
+          <t>The Access Bank UK Limited - KM1 Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000 (conv. from USD)</t>
+          <t>The Bank's own published KM1 key-metrics template, in its own row order, row numbers, labels and precision. Amounts in US DOLLARS ($'000) as published - this sheet is NOT converted to sterling, unlike the other Pillar 3 sheets in this workbook. Each column is taken from that year's own edition; FY2021 was recovered from an image. See the sources note for the six rows on which a later edition's comparative disagrees with the year's own edition.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -8066,46 +8190,736 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>599900.9</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>531687.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>402448.5</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>279437.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>248093.1</v>
-      </c>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
     </row>
-    <row r="6" ht="130" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-No FY2024 Pillar 3 Disclosures document exists. Re-verified 15 September 2026: nine filename permutations under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/09, 2025/12, 2026/01, 2026/06, 2026/07 folders) all return the site's 404 page, and a Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest being the 2023 edition. The Bank's HTML pages return HTTP 403 to both curl and automated fetchers (Cloudflare), so the CDN and Wayback are the only routes; both agree. The Bank publishes its Pillar 3 roughly 18 months after year-end (the 2023 edition was uploaded in the 2025/06 folder), so a FY2024 edition would be expected around mid-to-late 2026.
-For FY2024 the Annual Report substitutes ONLY where the basis is verified identical. The AR's Note 27g capital table is the same basis as the Pillar 3: its FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital', matching the CET1 = Tier 1 = Total capital treatment used in every other year. The AR's Tier 1 Capital Ratio (20.18%) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
-NOT substituted for FY2024, and left blank rather than derived: Total RWAs (the AR gives no RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m); Leverage Ratio (the AR discloses no leverage ratio and no leverage exposure measure - total assets of $6,125.4m is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (the AR contains no NSFR or stable-funding disclosure at all - 'stable funding' returns zero hits in the document). FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1  Common Equity Tier 1 (CET1) capital ($'000)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>676944</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>486842</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>377827</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>338920</v>
+      </c>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2  Tier 1 capital ($'000)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>676944</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>486842</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>377827</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>338920</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3  Total capital ($'000)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>676944</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>486842</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>377827</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>338920</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4  Total risk-weighted exposure amount ($'000)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>3024867</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2459345</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1726764</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1841957</v>
+      </c>
+      <c r="G9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>5  Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6  Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7  Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a  Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>7.69%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d  Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>15.69%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>8  Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>9  Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>11  Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a  Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>15.7%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>18.21%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>12  CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>6.19%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>13  Total exposure measure excluding claims on central banks ($'000)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n">
+        <v>4246733</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>14  Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>15.9%</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>13  Total Basel III Leverage Ratio exposure method ($'000)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n">
+        <v>4061990</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>3379955</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>2595307</v>
+      </c>
+      <c r="G26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>14  Basel III Leverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>11.18%</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>13.07%</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>15  Total high-quality liquid assets (HQLA) (Weighted value - average) ($'000)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n">
+        <v>902038</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>1053232</v>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>UK 16a  Cash outflows - Total weighted value ($'000)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n">
+        <v>987015</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>935189</v>
+      </c>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>UK 16b  Cash inflows - Total weighted value ($'000)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n">
+        <v>896548</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>732155</v>
+      </c>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>16  Total net cash outflows (adjusted value) ($'000)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n">
+        <v>246754</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>233797</v>
+      </c>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>17  Liquidity coverage ratio (%) (average of preceding twelve months)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>365.6%</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>450.5%</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>343.85%</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>346.76%</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>18  Total available stable funding ($'000)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n">
+        <v>1878935</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>1467825</v>
+      </c>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>19  Total required stable funding ($'000)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n">
+        <v>1114383</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>992570</v>
+      </c>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>20  NSFR ratio (%) (average of preceding four quarters)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>168.6%</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>147.9%</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>213.70%</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>173.76%</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n"/>
+    </row>
+    <row r="39" ht="340" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited's own KM1 key-metrics template in EACH YEAR'S OWN Pillar 3 edition. Figures are in US DOLLARS ($'000) exactly as published and are NOT converted to sterling, unlike every other Pillar 3 sheet in this workbook - a KM1 reproduces a published template, so it keeps the published currency. All ratios are as printed, including the Bank's own precision (two decimals in the FY2020/FY2021 editions, one decimal from FY2022).
+ENTITY: a single basis in every year. Each edition states: "These disclosures relate only to The Access Bank UK Limited, which has no trading subsidiaries, and therefore does not report on a consolidated basis." No figure of the Nigerian parent (Access Bank Plc) or of Access Holdings Plc appears here.
+FY2023: Pillar 3 Disclosures 2023, p.6, Section 1.7 'UK KM1 - Key metrics template', column a (31-Dec-23) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2022: Pillar 3 Disclosures 2022, pp.6-7, Section 1.7 'KM1 - Key metrics template', 2022 column - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2021: Pillar 3 Disclosures 2021, p.7, Section 1.7 'KM1 - Key metrics template', Dec-21 column - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2020: Pillar 3 Disclosures 2020, p.7, Section 1.7 'Key Metrics', Dec-20 column - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+FY2021 WAS READ FROM AN IMAGE, NOT FROM TEXT. The FY2021 edition embeds its KM1 as a picture (an 861x637 bitmap) rather than as text, so every text extraction of that page returns the heading 'KM1 - Key metrics template' and the trailing note about 'the above ratios' with nothing in between. The page was rendered at 300dpi and read directly, and each figure was transcribed twice from two independent renderings - the full page and the embedded bitmap at its native resolution - which agree digit for digit. The same edition's CC1 and LR2 tables are ordinary text, which is why this table's absence from our extracts looked like an absence of disclosure. research/km1_inventory.jsonl currently records this document as NO_KM1_FOUND and is wrong on that point.
+WHY NO COLUMN IS TAKEN FROM A LATER EDITION'S COMPARATIVE - THIS BANK IS THE DEMONSTRATION.
+The FY2022 edition's 2021 comparative disagrees with the FY2021 edition's own Dec-21 column on six rows, while capital, RWAs, capital ratios and leverage agree exactly: UK 7a 7.69% against 6.1%, UK 7d 15.69% against 14.1%, UK 11a 18.21% against 16.6%, row 12 6.19% against 7.8%, row 17 343.85% against 370.6%, and row 20 213.70% against 196.8%. Both editions are internally consistent under the Bank's own printed definition that row 12 is the difference between the total capital ratio and the total SREP own funds requirement (21.88 - 15.69 = 6.19; 21.9 - 14.1 = 7.8), so the FY2021 SREP requirement was genuinely restated between editions rather than mistyped. Note also that the FY2022 edition's 2021 SREP figures coincide with the FY2021 edition's Dec-20 column (6.11 / 14.11 / 16.63) - a near-match of the kind that makes a wrongly-read column look entirely plausible. The figures above are each edition's own year.
+THE LEVERAGE ROWS CARRY TWO DIFFERENT CAPTIONS AND ARE NOT MERGED (the 1 January 2022 basis break).
+The FY2020, FY2021 and FY2022 editions caption rows 13 and 14 'Total Basel III Leverage Ratio exposure method' and 'Basel III Leverage ratio (%)'. The FY2023 edition captions the same row numbers 'Total exposure measure excluding claims on central banks' and 'Leverage ratio excluding claims on central banks'. Both captions are kept as separate rows above rather than run together as one series. The FY2022 figure is identical under either caption (4,061,990), which is precisely why merging them would look safe.
+ROW SETS DIFFER BY EDITION - THESE BLANKS ARE NOT-PRINTED, NOT NOT-FOUND.
+Rows 15, UK 16a, UK 16b, 16, 18 and 19 appear only in the FY2022 and FY2023 editions; the FY2021 and FY2020 editions disclose liquidity as a single LCR ratio row and a single NSFR ratio row. The FY2020 edition additionally prints no UK 7a, UK 7d, UK 11a or row 12. Neither edition prints UK 7b or UK 7c in any year - this Bank discloses only the CET1 and total SREP requirements.
+SOURCE DEFECTS, REPRODUCED AND FLAGGED (rule 7).
+1. The FY2020 edition captions its risk-weighted assets section '($m)' while the figures printed under it are plainly $'000 (1,841,957 is $1.84bn, not $1.84 trillion); its leverage row is captioned '($m)' the same way. The figures are carried as $'000, the unit the magnitudes and every adjacent edition confirm, and the caption defect is recorded rather than silently corrected.
+2. The FY2020 edition's row labels are its own and differ from the template's: 'Common Equity Tier (CET 1)', 'TIer 1 Ratio (%)' (with that capitalisation), and row 11 as 'Total of bank CET1 specific buffer requirement'. Its section headings likewise read 'Available capital' and 'Additional CET 1 buffer requirement as a percentage of RWA'. The template's canonical labels are used for the sheet's rows because the row NUMBERS and measures are the Bank's own; the label variants are recorded here.
+3. The FY2023 edition prints the five-column template's column letters as 'a' and 'e' over 31-Dec-23 and 31-Dec-22 - two populated columns of a five-column template, not a two-column table.
+FY2024 AND FY2019 ARE BLANK, FOR DIFFERENT REASONS.
+FY2024: no FY2024 Pillar 3 edition exists. That finding is this script's own, recorded 2026-09-15 on positive evidence - nine filename permutations across six CDN upload folders, plus a Wayback CDX sweep of the whole domain filtered on 'pillar' returning exactly five documents, the newest being the 2023 edition - and it is retained here rather than re-derived. See p3_sources() for the detail and for what the Annual Report does and does not substitute.
+FY2019: the Bank's FY2019 Pillar 3 edition has not been located. The FY2020 edition prints a Dec-19 comparative column, and it is deliberately NOT used here for the reason demonstrated above. FY2019 therefore carries no column on this sheet, while the single-metric sheets continue to show that comparative under their own citation.
+EXPECTED VERIFIER OUTPUT - TWO DISAGREEMENTS THAT ARE CORRECT AND MUST NOT BE 'FIXED'.
+scripts/verify_workbook.py reports KM1 row 17 FY2021 (343.85%) and row 20 FY2021 (213.70%) as disagreeing with the LCR and NSFR sheets (370.6% and 196.8%). Both sides are deliberate and both are right for what they are: this sheet takes FY2021 from the FY2021 edition's own Dec-21 column, while those metric sheets cite the FY2022 edition's 2021 comparative, as their own source notes say. The gap IS the restatement documented above - the checker found it independently, from the other direction. Everything else reconciles, and the amount rows are skipped by design because this sheet is in USD and the metric sheets are in converted sterling.
+LATEST-EDITION CHECK, 2026-09-16 - BLOCKED, WHICH IS NOT THE SAME AS 'NONE NEWER' (map rule 9).
+The Bank's own website could not be read at all today. The homepage, the investor-relations page, sitemaps.xml (the filename robots.txt itself names) and every wp-json endpoint each returned HTTP 403 carrying a Cloudflare 'Just a moment...' JavaScript interstitial, including with a full desktop browser User-Agent - the technique that did defeat the Lloyds Banking Group block for Bank of Scotland does NOT work on this host. Static files are served normally (robots.txt 200 text/plain, and every cited PDF 200 application/pdf), so the block is on the HTML surface only. web.archive.org returned 'Temporarily Offline' throughout, so the archive route was unavailable rather than empty. 96 plausible 2024/2025 filenames under /wp-content/uploads/ returned nothing, which proves little given this Bank's filename variance (PILLAR-3-DISCLOSURES-2020-Clean, -2021-Final, -2022-Final, then PIllar-3-2023.pdf with a capital-I typo). CONCLUSION: the index could not be read, so no claim is made here about whether a newer edition exists. The 2026-09-15 evidence above remains the best available and should be re-run once the site or the archive is reachable.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8132,14 +8946,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — CET1 Ratio</t>
+          <t>The Access Bank UK Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000 (conv. from USD)</t>
         </is>
       </c>
     </row>
@@ -8183,33 +8997,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.18%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>21.88%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>18.40%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>599900.9</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>531687.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>402448.5</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>279437.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>248093.1</v>
       </c>
       <c r="G4" s="6" t="n"/>
     </row>
@@ -8242,7 +9046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8257,14 +9061,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — Tier 1 Capital</t>
+          <t>The Access Bank UK Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000 (conv. from USD)</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -8308,35 +9112,38 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>599900.9</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>531687.1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>402448.5</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>279437.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>248093.1</v>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
       </c>
       <c r="G4" s="6" t="n"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Equal to CET1 capital in every year - the Bank holds no Additional Tier 1 (AT1) instruments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="130" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
 FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
@@ -8351,9 +9158,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/ACCESS BANK UK FINANCIALS.xlsx
+++ b/banks/ACCESS BANK UK FINANCIALS.xlsx
@@ -4696,37 +4696,37 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in Access Bank UK Annual Report FY2025 (text search, 2026-09-19); no FY2025 Pillar 3 exists.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in Access Bank UK Annual Report FY2024 (text search, 2026-09-19); no FY2024 Pillar 3 exists.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2023 or Annual Report (text search, 2026-09-19).</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2022 or Annual Report (text search, 2026-09-19).</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2021 or Annual Report (text search, 2026-09-19).</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2020 or Annual Report (text search, 2026-09-19).</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in Access Bank UK Annual Report FY2019 (text search, 2026-09-19); FY2020 Pillar 3 (Dec-19 comparatives) has none.</t>
         </is>
       </c>
     </row>

--- a/banks/ACCESS BANK UK FINANCIALS.xlsx
+++ b/banks/ACCESS BANK UK FINANCIALS.xlsx
@@ -619,12 +619,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AF$18:$AL$18</f>
+              <f>'Overview'!$AF$18:$AK$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AF$19:$AL$19</f>
+              <f>'Overview'!$AF$19:$AK$19</f>
             </numRef>
           </val>
         </ser>
@@ -643,12 +643,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AF$18:$AL$18</f>
+              <f>'Overview'!$AF$18:$AK$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AF$20:$AL$20</f>
+              <f>'Overview'!$AF$20:$AK$20</f>
             </numRef>
           </val>
         </ser>
@@ -667,12 +667,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AF$18:$AL$18</f>
+              <f>'Overview'!$AF$18:$AK$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AF$21:$AL$21</f>
+              <f>'Overview'!$AF$21:$AK$21</f>
             </numRef>
           </val>
         </ser>
@@ -691,12 +691,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AF$18:$AL$18</f>
+              <f>'Overview'!$AF$18:$AK$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AF$22:$AL$22</f>
+              <f>'Overview'!$AF$22:$AK$22</f>
             </numRef>
           </val>
         </ser>
@@ -807,7 +807,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO26</f>
+              <f>'Overview'!AN26</f>
             </strRef>
           </tx>
           <spPr>
@@ -817,12 +817,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$25:$AV$25</f>
+              <f>'Overview'!$AO$25:$AU$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$26:$AV$26</f>
+              <f>'Overview'!$AO$26:$AU$26</f>
             </numRef>
           </val>
         </ser>
@@ -831,7 +831,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO27</f>
+              <f>'Overview'!AN27</f>
             </strRef>
           </tx>
           <spPr>
@@ -841,12 +841,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$25:$AV$25</f>
+              <f>'Overview'!$AO$25:$AU$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$27:$AV$27</f>
+              <f>'Overview'!$AO$27:$AU$27</f>
             </numRef>
           </val>
         </ser>
@@ -855,7 +855,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO28</f>
+              <f>'Overview'!AN28</f>
             </strRef>
           </tx>
           <spPr>
@@ -865,12 +865,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$25:$AV$25</f>
+              <f>'Overview'!$AO$25:$AU$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$28:$AV$28</f>
+              <f>'Overview'!$AO$28:$AU$28</f>
             </numRef>
           </val>
         </ser>
@@ -879,7 +879,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO29</f>
+              <f>'Overview'!AN29</f>
             </strRef>
           </tx>
           <spPr>
@@ -889,12 +889,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$25:$AV$25</f>
+              <f>'Overview'!$AO$25:$AU$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$29:$AV$29</f>
+              <f>'Overview'!$AO$29:$AU$29</f>
             </numRef>
           </val>
         </ser>
@@ -1004,7 +1004,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AY6</f>
+              <f>'Overview'!AX6</f>
             </strRef>
           </tx>
           <spPr>
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AY$5:$BD$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$6:$BF$6</f>
+              <f>'Overview'!$AY$6:$BD$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1037,7 +1037,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AY7</f>
+              <f>'Overview'!AX7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1055,12 +1055,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AY$5:$BD$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$7:$BF$7</f>
+              <f>'Overview'!$AY$7:$BD$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1070,7 +1070,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AY8</f>
+              <f>'Overview'!AX8</f>
             </strRef>
           </tx>
           <spPr>
@@ -1088,12 +1088,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AY$5:$BD$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$8:$BF$8</f>
+              <f>'Overview'!$AY$8:$BD$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1103,7 +1103,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AY9</f>
+              <f>'Overview'!AX9</f>
             </strRef>
           </tx>
           <spPr>
@@ -1121,12 +1121,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AY$5:$BD$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$9:$BF$9</f>
+              <f>'Overview'!$AY$9:$BD$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1136,7 +1136,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!AY10</f>
+              <f>'Overview'!AX10</f>
             </strRef>
           </tx>
           <spPr>
@@ -1154,12 +1154,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AY$5:$BD$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$10:$BF$10</f>
+              <f>'Overview'!$AY$10:$BD$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1169,7 +1169,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!AY11</f>
+              <f>'Overview'!AX11</f>
             </strRef>
           </tx>
           <spPr>
@@ -1187,12 +1187,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AZ$5:$BF$5</f>
+              <f>'Overview'!$AY$5:$BD$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AZ$11:$BF$11</f>
+              <f>'Overview'!$AY$11:$BD$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1667,7 +1667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF40"/>
+  <dimension ref="A1:BD40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1724,8 +1724,6 @@
     <col hidden="1" width="13" customWidth="1" min="54" max="54"/>
     <col hidden="1" width="13" customWidth="1" min="55" max="55"/>
     <col hidden="1" width="13" customWidth="1" min="56" max="56"/>
-    <col hidden="1" width="13" customWidth="1" min="57" max="57"/>
-    <col hidden="1" width="13" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1826,37 +1824,32 @@
           <t>FY2025</t>
         </is>
       </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1886,11 +1879,16 @@
       <c r="G6" s="5" t="n">
         <v>1755034.4</v>
       </c>
-      <c r="H6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
+        <v>1892202.4</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1892202.4</v>
       </c>
       <c r="M6" t="n">
         <v>1755034.4</v>
@@ -1910,27 +1908,27 @@
       <c r="R6" t="n">
         <v>3826593.5</v>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
+      <c r="AY6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>21.88</v>
+      </c>
       <c r="BA6" t="n">
-        <v>18.4</v>
+        <v>19.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>21.88</v>
+        <v>22.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>19.8</v>
+        <v>20.18</v>
       </c>
       <c r="BD6" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="BF6" t="n">
         <v>11.78</v>
       </c>
     </row>
@@ -1958,11 +1956,16 @@
       <c r="G7" s="5" t="n">
         <v>651852.8</v>
       </c>
-      <c r="H7" s="5" t="n"/>
+      <c r="H7" s="5" t="n">
+        <v>661685.5</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Loans and advances to customers</t>
         </is>
+      </c>
+      <c r="L7" t="n">
+        <v>661685.5</v>
       </c>
       <c r="M7" t="n">
         <v>651852.8</v>
@@ -1982,27 +1985,27 @@
       <c r="R7" t="n">
         <v>1258199.7</v>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
+      <c r="AY7" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>21.88</v>
+      </c>
       <c r="BA7" t="n">
-        <v>18.4</v>
+        <v>19.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>21.88</v>
+        <v>22.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>19.8</v>
+        <v>20.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="BF7" t="n">
         <v>19.27</v>
       </c>
     </row>
@@ -2030,11 +2033,16 @@
       <c r="G8" s="5" t="n">
         <v>641605.3</v>
       </c>
-      <c r="H8" s="5" t="n"/>
+      <c r="H8" s="5" t="n">
+        <v>591188.3</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Customer deposits</t>
         </is>
+      </c>
+      <c r="L8" t="n">
+        <v>591188.3</v>
       </c>
       <c r="M8" t="n">
         <v>641605.3</v>
@@ -2054,27 +2062,27 @@
       <c r="R8" t="n">
         <v>1301646.3</v>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
+      <c r="AY8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>21.88</v>
+      </c>
       <c r="BA8" t="n">
-        <v>18.4</v>
+        <v>19.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>21.88</v>
+        <v>22.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>19.8</v>
+        <v>20.18</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="BF8" t="n">
         <v>19.27</v>
       </c>
     </row>
@@ -2102,11 +2110,16 @@
       <c r="G9" s="5" t="n">
         <v>249045.8</v>
       </c>
-      <c r="H9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
+        <v>247508.2</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
+      </c>
+      <c r="L9" t="n">
+        <v>247508.2</v>
       </c>
       <c r="M9" t="n">
         <v>249045.8</v>
@@ -2126,37 +2139,37 @@
       <c r="R9" t="n">
         <v>853251</v>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
+      <c r="AY9" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>11.18</v>
+      </c>
       <c r="BA9" t="n">
-        <v>13.07</v>
+        <v>12</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD9" t="n">
         <v>15.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="AY10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
+      <c r="AZ10" t="n">
+        <v>370.6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>450.5</v>
+      </c>
       <c r="BB10" t="n">
-        <v>370.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>450.5</v>
-      </c>
-      <c r="BD10" t="n">
         <v>365.6</v>
       </c>
     </row>
@@ -2166,18 +2179,18 @@
           <t>Profit &amp; Loss Summary (£'000)</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
+      <c r="AZ11" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>147.9</v>
+      </c>
       <c r="BB11" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>147.9</v>
-      </c>
-      <c r="BD11" t="n">
         <v>168.6</v>
       </c>
     </row>
@@ -2282,11 +2295,16 @@
       <c r="G13" s="5" t="n">
         <v>32870.6</v>
       </c>
-      <c r="H13" s="5" t="n"/>
+      <c r="H13" s="5" t="n">
+        <v>66715.39999999999</v>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>Total operating income / Net operating income</t>
         </is>
+      </c>
+      <c r="V13" t="n">
+        <v>66715.39999999999</v>
       </c>
       <c r="W13" t="n">
         <v>32870.6</v>
@@ -2331,11 +2349,16 @@
       <c r="G14" s="5" t="n">
         <v>-19761.1</v>
       </c>
-      <c r="H14" s="5" t="n"/>
+      <c r="H14" s="5" t="n">
+        <v>-21951.5</v>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>Total operating expense</t>
         </is>
+      </c>
+      <c r="V14" t="n">
+        <v>-21951.5</v>
       </c>
       <c r="W14" t="n">
         <v>-19761.1</v>
@@ -2380,11 +2403,16 @@
       <c r="G15" s="5" t="n">
         <v>10520.4</v>
       </c>
-      <c r="H15" s="5" t="n"/>
+      <c r="H15" s="5" t="n">
+        <v>34694.4</v>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
+      </c>
+      <c r="V15" t="n">
+        <v>34694.4</v>
       </c>
       <c r="W15" t="n">
         <v>10520.4</v>
@@ -2448,42 +2476,32 @@
           <t>FY2020</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2020</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2511,25 +2529,24 @@
         <v>249045.8</v>
       </c>
       <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>Opening equity</t>
         </is>
       </c>
+      <c r="AG19" t="n">
+        <v>249045.8</v>
+      </c>
       <c r="AH19" t="n">
-        <v>249045.8</v>
+        <v>281638</v>
       </c>
       <c r="AI19" t="n">
-        <v>281638</v>
+        <v>405955.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>405955.2</v>
+        <v>535897.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>535897.1</v>
-      </c>
-      <c r="AL19" t="n">
         <v>627171.1</v>
       </c>
     </row>
@@ -2557,28 +2574,27 @@
       <c r="G20" s="5" t="n">
         <v>10331.9</v>
       </c>
-      <c r="H20" s="5" t="n"/>
       <c r="AE20" t="inlineStr">
         <is>
           <t>Total comprehensive income for the year</t>
         </is>
       </c>
+      <c r="AF20" t="n">
+        <v>10331.9</v>
+      </c>
       <c r="AG20" t="n">
-        <v>10331.9</v>
+        <v>29509.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>29509.4</v>
+        <v>36629.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>36629.5</v>
+        <v>91378.3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>91378.3</v>
+        <v>98894.39999999999</v>
       </c>
       <c r="AK20" t="n">
-        <v>98894.39999999999</v>
-      </c>
-      <c r="AL20" t="n">
         <v>84614.60000000001</v>
       </c>
     </row>
@@ -2606,28 +2622,27 @@
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="5" t="n"/>
       <c r="AE21" t="inlineStr">
         <is>
           <t>Other equity movements, net</t>
         </is>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>52580.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>52580.5</v>
+        <v>62347.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>62347.9</v>
+        <v>-18624.9</v>
       </c>
       <c r="AK21" t="n">
-        <v>-18624.9</v>
-      </c>
-      <c r="AL21" t="n">
         <v>190188.7</v>
       </c>
     </row>
@@ -2655,28 +2670,27 @@
       <c r="G22" s="5" t="n">
         <v>249045.8</v>
       </c>
-      <c r="H22" s="5" t="n"/>
       <c r="AE22" t="inlineStr">
         <is>
           <t>Closing equity</t>
         </is>
       </c>
+      <c r="AF22" t="n">
+        <v>249045.8</v>
+      </c>
       <c r="AG22" t="n">
-        <v>249045.8</v>
+        <v>281638</v>
       </c>
       <c r="AH22" t="n">
-        <v>281638</v>
+        <v>405955.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>405955.2</v>
+        <v>535897.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>535897.1</v>
+        <v>627171.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>627171.1</v>
-      </c>
-      <c r="AL22" t="n">
         <v>853251</v>
       </c>
     </row>
@@ -2728,37 +2742,37 @@
           <t>FY2019</t>
         </is>
       </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2020</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2788,28 +2802,33 @@
       <c r="G26" s="5" t="n">
         <v>-307926.5</v>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="AO26" t="inlineStr">
+      <c r="H26" s="5" t="n">
+        <v>-173436.3</v>
+      </c>
+      <c r="AN26" t="inlineStr">
         <is>
           <t>Net cash from/(used in) operating activities</t>
         </is>
       </c>
+      <c r="AO26" t="n">
+        <v>-173436.3</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-307926.5</v>
+      </c>
       <c r="AQ26" t="n">
-        <v>-307926.5</v>
+        <v>455703.9</v>
       </c>
       <c r="AR26" t="n">
-        <v>455703.9</v>
+        <v>117981.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>117981.6</v>
+        <v>49148.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>49148.5</v>
+        <v>914715.2</v>
       </c>
       <c r="AU26" t="n">
-        <v>914715.2</v>
-      </c>
-      <c r="AV26" t="n">
         <v>-656945.3</v>
       </c>
     </row>
@@ -2837,28 +2856,33 @@
       <c r="G27" s="5" t="n">
         <v>46043.3</v>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="AO27" t="inlineStr">
+      <c r="H27" s="5" t="n">
+        <v>-17280.2</v>
+      </c>
+      <c r="AN27" t="inlineStr">
         <is>
           <t>Net cash from/(used in) investing activities</t>
         </is>
       </c>
+      <c r="AO27" t="n">
+        <v>-17280.2</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>46043.3</v>
+      </c>
       <c r="AQ27" t="n">
-        <v>46043.3</v>
+        <v>-184838.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>-184838.2</v>
+        <v>-85936.39999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>-85936.39999999999</v>
+        <v>-250467.3</v>
       </c>
       <c r="AT27" t="n">
-        <v>-250467.3</v>
+        <v>-1018064.7</v>
       </c>
       <c r="AU27" t="n">
-        <v>-1018064.7</v>
-      </c>
-      <c r="AV27" t="n">
         <v>558230.1</v>
       </c>
     </row>
@@ -2886,28 +2910,33 @@
       <c r="G28" s="5" t="n">
         <v>-1036.9</v>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="AO28" t="inlineStr">
+      <c r="H28" s="5" t="n">
+        <v>26239.7</v>
+      </c>
+      <c r="AN28" t="inlineStr">
         <is>
           <t>Net cash from/(used in) financing activities</t>
         </is>
       </c>
+      <c r="AO28" t="n">
+        <v>26239.7</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-1036.9</v>
+      </c>
       <c r="AQ28" t="n">
-        <v>-1036.9</v>
+        <v>-841.1</v>
       </c>
       <c r="AR28" t="n">
-        <v>-841.1</v>
+        <v>51487.3</v>
       </c>
       <c r="AS28" t="n">
-        <v>51487.3</v>
+        <v>63364.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>63364.5</v>
+        <v>-22938.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>-22938.6</v>
-      </c>
-      <c r="AV28" t="n">
         <v>188436.3</v>
       </c>
     </row>
@@ -2935,28 +2964,33 @@
       <c r="G29" s="5" t="n">
         <v>117322.9</v>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="AO29" t="inlineStr">
+      <c r="H29" s="5" t="n">
+        <v>376653.1</v>
+      </c>
+      <c r="AN29" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of year</t>
         </is>
       </c>
+      <c r="AO29" t="n">
+        <v>376653.1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>117322.9</v>
+      </c>
       <c r="AQ29" t="n">
-        <v>117322.9</v>
+        <v>392792.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>392792.6</v>
+        <v>524595.1</v>
       </c>
       <c r="AS29" t="n">
-        <v>524595.1</v>
+        <v>364263.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>364263.6</v>
+        <v>241803</v>
       </c>
       <c r="AU29" t="n">
-        <v>241803</v>
-      </c>
-      <c r="AV29" t="n">
         <v>316267.8</v>
       </c>
     </row>
@@ -3003,11 +3037,6 @@
           <t>FY2020</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3045,7 +3074,6 @@
           <t>18.40%</t>
         </is>
       </c>
-      <c r="H33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3083,7 +3111,6 @@
           <t>18.40%</t>
         </is>
       </c>
-      <c r="H34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3121,7 +3148,6 @@
           <t>18.40%</t>
         </is>
       </c>
-      <c r="H35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3151,7 +3177,6 @@
           <t>13.07%</t>
         </is>
       </c>
-      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -3177,7 +3202,6 @@
         </is>
       </c>
       <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -3203,7 +3227,6 @@
         </is>
       </c>
       <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="7" t="inlineStr">

--- a/banks/ACCESS BANK UK FINANCIALS.xlsx
+++ b/banks/ACCESS BANK UK FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2172,6 +2172,12 @@
       <c r="BB10" t="n">
         <v>365.6</v>
       </c>
+      <c r="BC10" t="n">
+        <v>176.65</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>199.46</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3184,8 +3190,16 @@
           <t>LCR</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>199.46%</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>176.65%</t>
+        </is>
+      </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
           <t>365.6%</t>
@@ -3228,7 +3242,7 @@
       </c>
       <c r="G38" s="6" t="n"/>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="104" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation. All £ figures are converted from the Bank's native USD reporting (see Cash Flow Statement sheet's FX conversion note) - this conversion was not explicitly requested for this bank but applied for consistency with the rest of the series. This workbook covers FY2019-FY2025; the statement sheets run to FY2025 (extended 18 September 2026 from the Bank's Report &amp; Financial Statements 2025), while the Pillar 3 template sheets stop at FY2023 because no FY2024 and no FY2025 Pillar 3 edition exists - see those sheets' source notes for the evidence and the expected publication lag. Where the FY2024 and FY2025 Annual Reports themselves disclose a capital figure on the Pillar 3 basis it is carried (CET1/Tier 1/Total capital ratios, Tier 1 and Total capital amounts, point-in-time LCR); RWAs, leverage and NSFR are blank for those two years because neither report discloses them. FY2020 LCR/NSFR are blank too (not found in any source). FY2025 is also the first year the CET1 ratio diverges from the Tier 1 ratio (11.78% against 19.27%), following the Bank's first AT1 issuance. 'Total operating income / Net operating income' uses each year's Net operating income (after ECL), the one operating-income-level figure disclosed consistently across all 5 years (see Asset Quality sheet's presentation note on the P&amp;L structure change). Opening equity for FY2020 is not shown (no 31 December 2019 GBP/USD rate sourced) - see the Statement of Changes in Equity sheet's FX caveat.</t>
@@ -3250,7 +3264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3338,14 +3352,14 @@
         <v>248093.1</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="52" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Equal to CET1 capital for FY2020-FY2024 - the Bank held no Additional Tier 1 (AT1) instruments in those years. FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
+    <row r="7" ht="234" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -3356,17 +3370,33 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="286" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="169" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3378,7 +3408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3478,14 +3508,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="39" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
+    <row r="7" ht="234" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -3496,17 +3526,33 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="286" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="169" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3518,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3606,14 +3652,14 @@
         <v>248093.1</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="65" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Equal to Tier 1 capital in every year shown, including FY2025 - the Bank's own capital-management note states in every edition that 'the Bank's regulatory capital consists only of Tier 1 capital', so it holds no Tier 2. FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%. The AT1 issuance therefore splits CET1 away from Tier 1 without splitting Tier 1 away from Total capital.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
+    <row r="7" ht="234" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -3624,17 +3670,33 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="286" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="169" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3646,7 +3708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3746,14 +3808,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="39" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Equal to the Tier 1 ratio in every year shown - no Tier 2 instruments. FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
+    <row r="7" ht="234" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -3764,17 +3826,33 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="286" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="169" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3786,7 +3864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3878,7 +3956,7 @@
         <v>1348332.5</v>
       </c>
     </row>
-    <row r="6" ht="130" customHeight="1">
+    <row r="6" ht="234" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -3889,16 +3967,32 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="286" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="169" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3910,7 +4004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4112,21 +4206,29 @@
         <v>1348332.5</v>
       </c>
     </row>
-    <row r="12" ht="170" customHeight="1">
+    <row r="12" ht="247" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited's own OV1 (Overview of risk weighted exposure amounts) table, converted from USD to £ at that year's BoE spot rate:
 FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 4.3, OV1) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
 FY2021 &amp; FY2020: Pillar 3 Disclosures 2022, p.15 (Section 4.3, OV1) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
 ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead read through a text-extraction proxy (2026-09-18) and via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. LATEST-EDITION CHECK, 18 SEPTEMBER 2026: the Bank's 'Our Reports' page lists a FY2025 Annual Report and a FY2025 Report &amp; Financial Statements (both uploaded to the Bank's CDN in its 2026/06 folder; the financial statements were signed 23 April 2026 and the PDF was produced 15 June 2026), and this workbook was extended to FY2025 from them on that date. The newest Pillar 3 Disclosures edition on that same page is still the 2023 one - no FY2024 and no FY2025 Pillar 3 edition exists as at 18 September 2026 (see the Pillar 3 sheets' source notes for the evidence). This workbook therefore covers FY2019-FY2025 - 7 years of statements, but Pillar 3 template metrics only to FY2023; FY2024 and FY2025 Pillar 3 cells are filled ONLY from the Annual Report where the Bank itself discloses the figure on the same basis, and are otherwise blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed. THAT CHOICE MATTERS MUCH MORE FROM FY2025: the Group acquired control of AfrAsia Bank Limited (Mauritius) during 2025 and consolidated it for the first time, so Group total assets ($11,617.1m) are now more than double the Bank's ($5,146.0m). Every FY2025 figure in this workbook is the BANK column, on the same basis as FY2019-FY2024; no Group figure is mixed in.
-UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.
+UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="234" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all average 1.2782; FY2025 spot 1.3448 / average 1.3193 (the same FY2025 pair already used in build_zenith.py); FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
 No FY2024 and no FY2025 Pillar 3 Disclosures document exists (same gap documented on the Pillar 3 metric sheets, re-verified against the Bank's own Reports page on 18 September 2026) - those cells are blank rather than guessed, and neither Annual Report prints an RWA breakdown or an RWA total. The Bank has no market risk RWA requirement in any year shown (its own Pillar 3 reports state market risk is below the CRR de minimis threshold - it holds no trading book) - not a missing-disclosure gap, a genuine nil. 'Of which: credit valuation adjustment (CVA)' is a memo sub-item already included WITHIN 'Counterparty credit risk (CCR)' above it (per the OV1 template's own structure), not an additional component - it will appear to double-count against the Total row in a naive DATA-sum reconciliation check; this is expected and matches the Bank's own table structure.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4139,7 +4241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4226,7 +4328,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Leverage ratio (%)</t>
+          <t>Leverage ratio (%) - FY2022 onward excluding claims on central banks (UK KM1); FY2020-FY2021 including claims on central banks (UK LR2); see note</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -4260,14 +4362,14 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="39" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: FY2020/FY2021 source tables (UK LR2, in the FY2021 Pillar 3 report) label this 'including claims on central banks'; FY2022 onward (UK KM1 template) labels it 'excluding claims on central banks'. Despite the differing labels, the FY2021 figure is identical (3,379,955) in both the FY2021 report's own table and the FY2022 report's comparative column, so this appears to be inconsistent wording by the Bank rather than a genuine methodology change - shown here as a single continuous row, flagged for visibility.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="130" customHeight="1">
+    <row r="8" ht="234" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -4278,17 +4380,33 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="286" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="169" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4300,7 +4418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4441,14 +4559,14 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="117" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Note: TWO DIFFERENT BASES, deliberately kept on separate rows. The KM1 row is the Bank's 'average of preceding twelve months' figure and is the basis used for FY2021-FY2023. The point-in-time row is the Bank's year-end spot LCR. They are NOT comparable: for FY2023 the Bank discloses BOTH - 365.6% on the KM1 average basis (Pillar 3 Disclosures 2023, p.6 row 17) and 275.5% at 31 December 2023 (same document, Section 8 narrative), a 90-point gap. FY2024 and FY2025 have no Pillar 3 report, so for each of those years only the point-in-time figure exists (176.65% per the Annual Report 2024 KPI table; 199.46% per the Report &amp; Financial Statements 2025 KPI table, p.4, Bank 2025 column); both are shown on the point-in-time row and the KM1 average row is left BLANK for FY2024 and FY2025 rather than continued with a different-basis number. An earlier revision of this workbook placed 176.65% directly in the KM1 average row, which made the ratio appear to fall 365.6% -&gt; 176.65%; the like-for-like point-in-time move is 275.47% -&gt; 176.65%. FY2021's $ breakdown (HQLA/net cash outflows) is sourced from the FY2022 Pillar 3 report's comparative column - the FY2021 Pillar 3 report itself only states a single narrative LCR percentage (343.9%), not a KM1-style table with a $ breakdown; that narrative figure is again a different convention from the 370.6% KM1 figure shown here. FY2020 not found in any source.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="130" customHeight="1">
+    <row r="10" ht="260" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -4459,17 +4577,33 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="325" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="182" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4481,7 +4615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4606,14 +4740,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021's $ breakdown is sourced from the FY2022 Pillar 3 report's comparative column (the FY2021 report itself does not tabulate NSFR). FY2020 not found in any source.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="130" customHeight="1">
+    <row r="9" ht="260" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -4624,15 +4758,31 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="325" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="182" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A9:F9"/>
   </mergeCells>
@@ -4646,7 +4796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4753,14 +4903,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: No MREL disclosure (numeric or qualitative) or UK KM2 template found in any year's Pillar 3 report - not explicitly stated as an exemption, but consistent with the Bank's small size relative to typical MREL-in-scope thresholds.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="234" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -4771,7 +4921,14 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="403" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
 For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
@@ -4779,8 +4936,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4793,7 +4951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -5754,7 +5912,7 @@
         <v>1892202.4</v>
       </c>
     </row>
-    <row r="43" ht="260" customHeight="1">
+    <row r="43" ht="364" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited's own Statement of Financial Position (Bank column), converted from USD to £ per the FX conversion note on the Cash Flow Statement sheet:
@@ -5770,7 +5928,14 @@
 FY2020: Report and Statutory Accounts 2021, Note 13 'Investment securities' (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
 FY2019: Report and Statutory Accounts 2019, Note 12 'Investment securities', p.27 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
 ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead read through a text-extraction proxy (2026-09-18) and via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. LATEST-EDITION CHECK, 18 SEPTEMBER 2026: the Bank's 'Our Reports' page lists a FY2025 Annual Report and a FY2025 Report &amp; Financial Statements (both uploaded to the Bank's CDN in its 2026/06 folder; the financial statements were signed 23 April 2026 and the PDF was produced 15 June 2026), and this workbook was extended to FY2025 from them on that date. The newest Pillar 3 Disclosures edition on that same page is still the 2023 one - no FY2024 and no FY2025 Pillar 3 edition exists as at 18 September 2026 (see the Pillar 3 sheets' source notes for the evidence). This workbook therefore covers FY2019-FY2025 - 7 years of statements, but Pillar 3 template metrics only to FY2023; FY2024 and FY2025 Pillar 3 cells are filled ONLY from the Annual Report where the Bank itself discloses the figure on the same basis, and are otherwise blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed. THAT CHOICE MATTERS MUCH MORE FROM FY2025: the Group acquired control of AfrAsia Bank Limited (Mauritius) during 2025 and consolidated it for the first time, so Group total assets ($11,617.1m) are now more than double the Bank's ($5,146.0m). Every FY2025 figure in this workbook is the BANK column, on the same basis as FY2019-FY2024; no Group figure is mixed in.
-UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.
+UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="403" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all average 1.2782; FY2025 spot 1.3448 / average 1.3193 (the same FY2025 pair already used in build_zenith.py); FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
 PRESENTATION NOTE: The Bank column (entity-level) is used throughout for consistency with the Cash Flow Statement sheet - Bank and Group are identical for FY2020-FY2023 (no subsidiary existed) and differ only immaterially for FY2024 (following the Access Bank Malta investment - see Investment in Subsidiary note). The Balance Sheet's line-item structure changed between report vintages: FY2024/FY2023 (AR2024) present 'Money market placements', 'Investment in subsidiary', 'Deferred tax liability' and a 'Prepaid corporation tax' asset as separate lines not present in earlier years; FY2022 (AR2022)/FY2021/FY2020 group these differently (e.g. a single 'Cash at bank' line, no separate money-market-placements or investment-securities split visible pre-FY2021 in the same granularity). Each year's own as-reported labels/granularity are preserved rather than forced into a common shape - blank cells indicate that year's report did not disclose that specific line. The P&amp;L's structure also changed: FY2024/FY2023 use a 'Total operating income' / 'Net operating income' (after ECL) structure; FY2022/FY2021/FY2020 use a similar shape but without the 'Total operating income' subtotal line (ECL is deducted one step later, after 'Other income', directly into 'Net operating income').
 FY2025 CHANGED THE STRUCTURE AGAIN, and the new/changed lines are carried as their own rows rather than folded into the older ones:
@@ -5781,8 +5946,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A45:H45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5794,7 +5960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -6477,7 +6643,7 @@
         <v>34866.2</v>
       </c>
     </row>
-    <row r="30" ht="260" customHeight="1">
+    <row r="30" ht="390" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited's own Statement of Comprehensive Income (Bank column), converted from USD to £ per the FX conversion note on the Cash Flow Statement sheet:
@@ -6488,7 +6654,14 @@
 FY2019: Report and Statutory Accounts 2019, p.11 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
 ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead read through a text-extraction proxy (2026-09-18) and via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. LATEST-EDITION CHECK, 18 SEPTEMBER 2026: the Bank's 'Our Reports' page lists a FY2025 Annual Report and a FY2025 Report &amp; Financial Statements (both uploaded to the Bank's CDN in its 2026/06 folder; the financial statements were signed 23 April 2026 and the PDF was produced 15 June 2026), and this workbook was extended to FY2025 from them on that date. The newest Pillar 3 Disclosures edition on that same page is still the 2023 one - no FY2024 and no FY2025 Pillar 3 edition exists as at 18 September 2026 (see the Pillar 3 sheets' source notes for the evidence). This workbook therefore covers FY2019-FY2025 - 7 years of statements, but Pillar 3 template metrics only to FY2023; FY2024 and FY2025 Pillar 3 cells are filled ONLY from the Annual Report where the Bank itself discloses the figure on the same basis, and are otherwise blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed. THAT CHOICE MATTERS MUCH MORE FROM FY2025: the Group acquired control of AfrAsia Bank Limited (Mauritius) during 2025 and consolidated it for the first time, so Group total assets ($11,617.1m) are now more than double the Bank's ($5,146.0m). Every FY2025 figure in this workbook is the BANK column, on the same basis as FY2019-FY2024; no Group figure is mixed in.
 UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.
-FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all average 1.2782; FY2025 spot 1.3448 / average 1.3193 (the same FY2025 pair already used in build_zenith.py); FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
+FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all average 1.2782; FY2025 spot 1.3448 / average 1.3193 (the same FY2025 pair already used in build_zenith.py); FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="260" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 PRESENTATION NOTE: The Bank column (entity-level) is used throughout for consistency with the Cash Flow Statement sheet - Bank and Group are identical for FY2020-FY2023 (no subsidiary existed) and differ only immaterially for FY2024 (following the Access Bank Malta investment - see Investment in Subsidiary note). The Balance Sheet's line-item structure changed between report vintages: FY2024/FY2023 (AR2024) present 'Money market placements', 'Investment in subsidiary', 'Deferred tax liability' and a 'Prepaid corporation tax' asset as separate lines not present in earlier years; FY2022 (AR2022)/FY2021/FY2020 group these differently (e.g. a single 'Cash at bank' line, no separate money-market-placements or investment-securities split visible pre-FY2021 in the same granularity). Each year's own as-reported labels/granularity are preserved rather than forced into a common shape - blank cells indicate that year's report did not disclose that specific line. The P&amp;L's structure also changed: FY2024/FY2023 use a 'Total operating income' / 'Net operating income' (after ECL) structure; FY2022/FY2021/FY2020 use a similar shape but without the 'Total operating income' subtotal line (ECL is deducted one step later, after 'Other income', directly into 'Net operating income').
 FY2025 CHANGED THE STRUCTURE AGAIN, and the new/changed lines are carried as their own rows rather than folded into the older ones:
 - Balance Sheet: 'Other financial assets' / 'Other non-financial assets' and 'Other financial liabilities' / 'Other non-financial liabilities' are split onto separate faces of the statement from FY2025; FY2019-FY2024 print a single combined line each, so the combined rows are blank for FY2025 and the split rows blank for every earlier year. 'Convertible notes' is a new equity component, first issued in 2025 ($295.0m). The FY2025 edition also prints a 'Deferred tax asset' line and (for the Bank) a 'Corporation tax liability' line as a dash in both its own and its comparative column - nil in both years - so neither is carried as a row here; that is the Bank printing a nil, not a figure this workbook failed to find.
@@ -6498,7 +6671,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A30:H30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6511,7 +6685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7498,7 +7672,7 @@
         <v>853251</v>
       </c>
     </row>
-    <row r="45" ht="280" customHeight="1">
+    <row r="45" ht="325" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited's own Statement of Changes in Equity (Bank basis), converted from USD to £ (Balance rows at that date's BoE spot rate; movement rows at that calendar year's BoE average rate - same FX methodology as the Cash Flow Statement sheet):
@@ -7508,7 +7682,14 @@
 2020 movements: Report and Statutory Accounts 2021, p.16 (comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
 2019 movements: Report and Statutory Accounts 2019, p.13 - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
 ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead read through a text-extraction proxy (2026-09-18) and via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. LATEST-EDITION CHECK, 18 SEPTEMBER 2026: the Bank's 'Our Reports' page lists a FY2025 Annual Report and a FY2025 Report &amp; Financial Statements (both uploaded to the Bank's CDN in its 2026/06 folder; the financial statements were signed 23 April 2026 and the PDF was produced 15 June 2026), and this workbook was extended to FY2025 from them on that date. The newest Pillar 3 Disclosures edition on that same page is still the 2023 one - no FY2024 and no FY2025 Pillar 3 edition exists as at 18 September 2026 (see the Pillar 3 sheets' source notes for the evidence). This workbook therefore covers FY2019-FY2025 - 7 years of statements, but Pillar 3 template metrics only to FY2023; FY2024 and FY2025 Pillar 3 cells are filled ONLY from the Annual Report where the Bank itself discloses the figure on the same basis, and are otherwise blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed. THAT CHOICE MATTERS MUCH MORE FROM FY2025: the Group acquired control of AfrAsia Bank Limited (Mauritius) during 2025 and consolidated it for the first time, so Group total assets ($11,617.1m) are now more than double the Bank's ($5,146.0m). Every FY2025 figure in this workbook is the BANK column, on the same basis as FY2019-FY2024; no Group figure is mixed in.
-UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.
+UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="280" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all average 1.2782; FY2025 spot 1.3448 / average 1.3193 (the same FY2025 pair already used in build_zenith.py); FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
 EQUITY SHEET FX CAVEAT: because this roll-forward mixes point-in-time Balance rows (spot rate) with in-year movement rows (average rate) - the same two-rate approach used for the Cash Flow Statement - each period's £ closing balance will differ very slightly from £ opening balance + £ movements (unlike the Cash Flow Statement, this sheet has no natural 'FX translation' line to absorb the difference, so no plug row is shown here). The underlying USD figures (see rows above) tie out exactly in every period; this is purely a £ presentation artefact of using two different conversion rates, not a data quality issue.
 PRESENTATION NOTE: FY2022's own statement labels its 'Proceeds from shares issued' row as part of a combined 'Total comprehensive income for the year' total (which would overstate that label); this workbook instead reports 'Total comprehensive income for the year (2022)' as profit + OCI only (excluding the share issuance), with 'Proceeds from shares issued' shown as its own separate row immediately after - the Balance at 31 December 2022 row still ties to the sum of all rows in between, this is a relabeling for clarity only, not a change to any figure.</t>
@@ -7516,7 +7697,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7529,7 +7711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -8578,14 +8760,22 @@
 FY2019: Report and Statutory Accounts 2019, p.14 (Statement of Cash Flows) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
 Activity-total rows may be off by up to £0.1k from summing the visible line items above them, since each £ line is independently rounded to 1 decimal place before summing; the full statement ties exactly end-to-end via the net change, opening balance, exchange-rate-effect and translation-effect lines (verified to the penny in £'000 terms for FY2021-FY2024; FY2020 has no opening balance, see FX note).
 ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead read through a text-extraction proxy (2026-09-18) and via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. LATEST-EDITION CHECK, 18 SEPTEMBER 2026: the Bank's 'Our Reports' page lists a FY2025 Annual Report and a FY2025 Report &amp; Financial Statements (both uploaded to the Bank's CDN in its 2026/06 folder; the financial statements were signed 23 April 2026 and the PDF was produced 15 June 2026), and this workbook was extended to FY2025 from them on that date. The newest Pillar 3 Disclosures edition on that same page is still the 2023 one - no FY2024 and no FY2025 Pillar 3 edition exists as at 18 September 2026 (see the Pillar 3 sheets' source notes for the evidence). This workbook therefore covers FY2019-FY2025 - 7 years of statements, but Pillar 3 template metrics only to FY2023; FY2024 and FY2025 Pillar 3 cells are filled ONLY from the Annual Report where the Bank itself discloses the figure on the same basis, and are otherwise blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed. THAT CHOICE MATTERS MUCH MORE FROM FY2025: the Group acquired control of AfrAsia Bank Limited (Mauritius) during 2025 and consolidated it for the first time, so Group total assets ($11,617.1m) are now more than double the Bank's ($5,146.0m). Every FY2025 figure in this workbook is the BANK column, on the same basis as FY2019-FY2024; no Group figure is mixed in.
-UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.
+UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="340" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all average 1.2782; FY2025 spot 1.3448 / average 1.3193 (the same FY2025 pair already used in build_zenith.py); FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
 PRESENTATION NOTE: presentation differs slightly between report vintages, each year's own as-reported line items/labels are preserved rather than forced into a common shape. FY2023/FY2024 split lease payments into separate 'Lease payments principal' and 'Lease payments interest' rows; FY2020-FY2022 instead show a single combined 'Lease payments' row (FY2022's own report keeps the combined presentation even though FY2023's report restates FY2022 as a split comparative - FY2022's own report's combined figure is used here, per this project's convention of preferring each year's own report). A handful of line items differ by $1-$3 between a year's own primary statement and its appearance as the following year's comparative column (immaterial rounding, e.g. FY2021 'Operating cash flows before movements in working capital' is $86,336,098 in AR2021's own statement vs $86,336,099 in AR2022's comparative) - each year's own primary statement figure is used throughout.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A48:H48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8598,7 +8788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -9216,7 +9406,14 @@
 FY2020: Report and Statutory Accounts 2021, p.42 (Note 24d, comparative column) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/ACCESS_BANK_AR_2021_Accounts.pdf
 FY2019: Report and Statutory Accounts 2019, p.37 (Note 23d) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2020/07/ACCE3269_ACCESS_BANK_AR_2019_WEB.pdf
 ENTITY NOTE: The Access Bank UK Limited (Companies House 06365062, FRN 478415) is a UK subsidiary of Access Bank Plc (Nigeria); ultimate parent is Access Holdings Plc (Nigeria). Like Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited elsewhere in this workbook series, it prepares full IFRS financial statements with a genuine Statement of Cash Flows every year - no FRS 101/102 cash-flow exemption applies. The Bank's Own Funds consist entirely of Common Equity Tier 1 (CET1) capital (no AT1 or Tier 2 instruments), so CET1 capital = Tier 1 capital = Total capital in every year shown. The Bank's own website blocks automated page fetches (Cloudflare bot protection on its HTML pages, though direct PDF links work); its 'Our Reports' page was instead read through a text-extraction proxy (2026-09-18) and via multiple Wayback Machine snapshots (2022-2025) to locate every year's Annual Report and Pillar 3 Disclosures PDF. LATEST-EDITION CHECK, 18 SEPTEMBER 2026: the Bank's 'Our Reports' page lists a FY2025 Annual Report and a FY2025 Report &amp; Financial Statements (both uploaded to the Bank's CDN in its 2026/06 folder; the financial statements were signed 23 April 2026 and the PDF was produced 15 June 2026), and this workbook was extended to FY2025 from them on that date. The newest Pillar 3 Disclosures edition on that same page is still the 2023 one - no FY2024 and no FY2025 Pillar 3 edition exists as at 18 September 2026 (see the Pillar 3 sheets' source notes for the evidence). This workbook therefore covers FY2019-FY2025 - 7 years of statements, but Pillar 3 template metrics only to FY2023; FY2024 and FY2025 Pillar 3 cells are filled ONLY from the Annual Report where the Bank itself discloses the figure on the same basis, and are otherwise blank rather than guessed. From FY2024 the Bank's own Statement of Cash Flows is presented on both 'Bank' and 'Group' bases (following the acquisition of an interest in a subsidiary during 2024 - see 'Purchase of share in subsidiary' below); the Bank (entity-level) column is used throughout this workbook for consistency with every earlier year, when Bank and Group were identical since no subsidiary existed. THAT CHOICE MATTERS MUCH MORE FROM FY2025: the Group acquired control of AfrAsia Bank Limited (Mauritius) during 2025 and consolidated it for the first time, so Group total assets ($11,617.1m) are now more than double the Bank's ($5,146.0m). Every FY2025 figure in this workbook is the BANK column, on the same basis as FY2019-FY2024; no Group figure is mixed in.
-UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.
+UNIT PRECISION CHANGES AT FY2025: the FY2019-FY2024 editions print the primary statements in whole US dollars and were transcribed at that precision; the FY2025 edition prints them in $'000. FY2025 source figures below are therefore written as whole dollars with three trailing zeros - that is the precision the Bank published, not a rounding applied here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="300" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FX CONVERSION NOTE: The Access Bank UK Limited reports in US Dollars. This workbook converts every $ amount to £ for consistency with the rest of this series, following the same methodology established for SMBC Bank International plc, Zenith Bank (UK) Limited and United Bank for Africa (UK) Limited: point-in-time/balance figures (capital, RWA, leverage exposure, HQLA, cash balances) use the Bank of England GBP/USD SPOT rate as at that fiscal year-end (31 December); flow figures (every cash flow statement line item) use the AVERAGE of Bank of England rates over that calendar year - both via poundsterlinglive.com's published Bank of England archive. Rates used (£1 = $X): FY2020 spot 1.3661 / average 1.2837; FY2021 spot 1.3521 / average 1.3752; FY2022 spot 1.2097 / average 1.2362; FY2023 spot 1.2732 / average 1.2439; FY2024 spot 1.2515 / average 1.2782 - identical to the FY2021-FY2024 rates already used for Zenith Bank UK and UBA UK, since all average 1.2782; FY2025 spot 1.3448 / average 1.3193 (the same FY2025 pair already used in build_zenith.py); FY2019 spot 1.3210 / average 1.2767 (Bank of England series XUDLUSS, 31 December 2019; its published calendar-year GBP/USD average). All % ratios (CET1/Tier 1/Total Capital/Leverage/LCR/NSFR ratios) are shown EXACTLY as reported in USD and were NOT converted - a ratio is dimensionless and currency-invariant. Because stocks and flows are converted at different rates, the cash flow statement includes an explicit 'Effect of GBP/USD translation' reconciling line (FY2021-FY2024 only, computed programmatically from the actual converted figures) so opening + all flows + this line = closing exactly in £ terms for those years - this line is purely an artefact of £ translation and has no bearing on the Bank's underlying USD results. This conversion was not explicitly requested for this bank - applied for consistency with the rest of the series, following the same call already confirmed for Zenith Bank UK and UBA UK; flag if £'000 rather than the Bank's native US$'000 presentation is not what's wanted here.
 PRESENTATION NOTE: the loan-book-by-product split is NOT presented on a consistent basis across all 5 years - FY2024/FY2023 disclose a GROSS product split (Loans to corporates / secured on property / other secured personal loans, from Note 18/17); FY2022/FY2021/FY2020 only disclose a NET-of-allowance Retail/Corporate split (from the credit risk exposure table), not a gross one at that granularity - each row is labelled to make this explicit, and the 'Total loans and advances to customers' row for each year sums exactly to whichever rows are populated for that year (gross FY2023-24, net FY2020-22) - do not compare that total row directly across the gross/net boundary. The by-IFRS-9-stage breakdown below IS on a consistent gross basis for all 5 years and ties to each year's own Balance Sheet 'Loans and advances to customers' gross figure. FY2024's Stage 3 loss allowance coverage (0.3%) is much lower than FY2023's (28.7%) - both figures are as directly reported; the Bank's own notes attribute this to a large trade-finance Stage 3 exposure ($49.9m) that is substantially collateralised by credit insurance, so most of its gross balance is not provisioned for - flagged here for visibility rather than smoothed over. FY2025 reverses that: the credit insurance on the Bank's impaired trade loans fell from $46.4m to $1.2m, and Stage 3 coverage returns to 24.2%.
 ENTITY BASIS, AND WHY FY2025 IS EXPLICITLY THE BANK COLUMN. Through FY2024 the Bank and Group ECL tables were the same figures, which is why this sheet's subtitle says Group. From FY2025 they are not: the Group consolidated AfrAsia Bank Limited (Mauritius) for the first time and its gross customer loan book is $3,154.9m against the Bank's $1,712.7m. Every FY2025 figure on this sheet is the BANK column, matching the Bank basis used on every other sheet in this workbook and on every earlier year here.
@@ -9226,7 +9423,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A26:H26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9239,7 +9437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -10021,7 +10219,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="340" customHeight="1">
+    <row r="40" ht="390" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited's own KM1 key-metrics template in EACH YEAR'S OWN Pillar 3 edition. Figures are in US DOLLARS ($'000) exactly as published and are NOT converted to sterling, unlike every other Pillar 3 sheet in this workbook - a KM1 reproduces a published template, so it keeps the published currency. All ratios are as printed, including the Bank's own precision (two decimals in the FY2020/FY2021 editions, one decimal from FY2022).
@@ -10036,7 +10234,14 @@
 THE LEVERAGE ROWS CARRY TWO DIFFERENT CAPTIONS AND ARE NOT MERGED (the 1 January 2022 basis break).
 The FY2020, FY2021 and FY2022 editions caption rows 13 and 14 'Total Basel III Leverage Ratio exposure method' and 'Basel III Leverage ratio (%)'. The FY2023 edition captions the same row numbers 'Total exposure measure excluding claims on central banks' and 'Leverage ratio excluding claims on central banks'. Both captions are kept as separate rows above rather than run together as one series. The FY2022 figure is identical under either caption (4,061,990), which is precisely why merging them would look safe.
 ROW SETS DIFFER BY EDITION - THESE BLANKS ARE NOT-PRINTED, NOT NOT-FOUND.
-Rows 15, UK 16a, UK 16b, 16, 18 and 19 appear only in the FY2022 and FY2023 editions; the FY2021 and FY2020 editions disclose liquidity as a single LCR ratio row and a single NSFR ratio row. The FY2020 edition additionally prints no UK 7a, UK 7d, UK 11a or row 12. Neither edition prints UK 7b or UK 7c in any year - this Bank discloses only the CET1 and total SREP requirements.
+Rows 15, UK 16a, UK 16b, 16, 18 and 19 appear only in the FY2022 and FY2023 editions; the FY2021 and FY2020 editions disclose liquidity as a single LCR ratio row and a single NSFR ratio row. The FY2020 edition additionally prints no UK 7a, UK 7d, UK 11a or row 12. Neither edition prints UK 7b or UK 7c in any year - this Bank discloses only the CET1 and total SREP requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="390" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 SOURCE DEFECTS, REPRODUCED AND FLAGGED (rule 7).
 1. The FY2020 edition captions its risk-weighted assets section '($m)' while the figures printed under it are plainly $'000 (1,841,957 is $1.84bn, not $1.84 trillion); its leverage row is captioned '($m)' the same way. The figures are carried as $'000, the unit the magnitudes and every adjacent edition confirm, and the caption defect is recorded rather than silently corrected.
 2. The FY2020 edition's row labels are its own and differ from the template's: 'Common Equity Tier (CET 1)', 'TIer 1 Ratio (%)' (with that capitalisation), and row 11 as 'Total of bank CET1 specific buffer requirement'. Its section headings likewise read 'Available capital' and 'Additional CET 1 buffer requirement as a percentage of RWA'. The template's canonical labels are used for the sheet's rows because the row NUMBERS and measures are the Bank's own; the label variants are recorded here.
@@ -10055,8 +10260,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10068,7 +10274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -10158,14 +10364,14 @@
         <v>248093.1</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="65" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%. FY2025 is therefore BLANK on this sheet: the Annual Report's Capital Resources table builds to a single 'Total regulatory capital' under the heading 'Tier one capital' and prints no CET1 amount, and no FY2025 Pillar 3 edition exists. Subtracting the convertible notes from Tier 1 to manufacture a CET1 figure is refused - it would not reproduce the Bank's own 11.78% ratio and is not a disclosure the Bank made.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
+    <row r="7" ht="234" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -10176,17 +10382,33 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="286" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="169" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10198,7 +10420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -10298,14 +10520,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="39" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="130" customHeight="1">
+    <row r="7" ht="234" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
@@ -10316,17 +10538,33 @@
 FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
 FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="286" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="169" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/ACCESS BANK UK FINANCIALS.xlsx
+++ b/banks/ACCESS BANK UK FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3279,14 +3280,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — Tier 1 Capital</t>
+          <t>The Access Bank UK Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000 (conv. from USD)</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3330,32 +3331,44 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>586186</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>599900.9</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>531687.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>402448.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>279437.2</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>248093.1</v>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>11.78%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="39" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Equal to CET1 capital for FY2020-FY2024 - the Bank held no Additional Tier 1 (AT1) instruments in those years. FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
+          <t>Note: FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
         </is>
       </c>
     </row>
@@ -3423,14 +3436,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — Tier 1 Ratio</t>
+          <t>The Access Bank UK Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000 (conv. from USD)</t>
         </is>
       </c>
     </row>
@@ -3474,44 +3487,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>19.27%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.18%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>21.88%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>18.40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="39" customHeight="1">
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>586186</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>599900.9</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>531687.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>402448.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>279437.2</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>248093.1</v>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
+          <t>Note: Equal to CET1 capital for FY2020-FY2024 - the Bank held no Additional Tier 1 (AT1) instruments in those years. FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
         </is>
       </c>
     </row>
@@ -3579,14 +3580,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — Total Capital</t>
+          <t>The Access Bank UK Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000 (conv. from USD)</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3630,32 +3631,44 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>586186</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>599900.9</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>531687.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>402448.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>279437.2</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>248093.1</v>
-      </c>
-    </row>
-    <row r="5" ht="65" customHeight="1">
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>19.27%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="39" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Equal to Tier 1 capital in every year shown, including FY2025 - the Bank's own capital-management note states in every edition that 'the Bank's regulatory capital consists only of Tier 1 capital', so it holds no Tier 2. FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%. The AT1 issuance therefore splits CET1 away from Tier 1 without splitting Tier 1 away from Total capital.</t>
+          <t>Note: FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
         </is>
       </c>
     </row>
@@ -3723,14 +3736,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — Total Capital Ratio</t>
+          <t>The Access Bank UK Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000 (conv. from USD)</t>
         </is>
       </c>
     </row>
@@ -3774,44 +3787,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>19.27%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.18%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>21.88%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>18.40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="39" customHeight="1">
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>586186</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>599900.9</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>531687.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>402448.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>279437.2</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>248093.1</v>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Equal to the Tier 1 ratio in every year shown - no Tier 2 instruments. FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
+          <t>Note: Equal to Tier 1 capital in every year shown, including FY2025 - the Bank's own capital-management note states in every edition that 'the Bank's regulatory capital consists only of Tier 1 capital', so it holds no Tier 2. FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%. The AT1 issuance therefore splits CET1 away from Tier 1 without splitting Tier 1 away from Total capital.</t>
         </is>
       </c>
     </row>
@@ -3859,6 +3860,162 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>19.27%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>21.88%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>18.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="39" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Equal to the Tier 1 ratio in every year shown - no Tier 2 instruments. FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="234" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
+FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="286" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="169" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3998,7 +4155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4235,7 +4392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4412,7 +4569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4609,7 +4766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4785,161 +4942,6 @@
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A9:F9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in Access Bank UK Annual Report FY2025 (text search, 2026-09-19); no FY2025 Pillar 3 exists.</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in Access Bank UK Annual Report FY2024 (text search, 2026-09-19); no FY2024 Pillar 3 exists.</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2023 or Annual Report (text search, 2026-09-19).</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2022 or Annual Report (text search, 2026-09-19).</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2021 or Annual Report (text search, 2026-09-19).</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2020 or Annual Report (text search, 2026-09-19).</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure in Access Bank UK Annual Report FY2019 (text search, 2026-09-19); FY2020 Pillar 3 (Dec-19 comparatives) has none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No MREL disclosure (numeric or qualitative) or UK KM2 template found in any year's Pillar 3 report - not explicitly stated as an exemption, but consistent with the Bank's small size relative to typical MREL-in-scope thresholds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="234" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
-FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
-FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="403" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
-NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5949,6 +5951,161 @@
   <mergeCells count="2">
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A45:H45"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in Access Bank UK Annual Report FY2025 (text search, 2026-09-19); no FY2025 Pillar 3 exists.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in Access Bank UK Annual Report FY2024 (text search, 2026-09-19); no FY2024 Pillar 3 exists.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2023 or Annual Report (text search, 2026-09-19).</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2022 or Annual Report (text search, 2026-09-19).</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2021 or Annual Report (text search, 2026-09-19).</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or KM2 in Access Bank UK Pillar 3 FY2020 or Annual Report (text search, 2026-09-19).</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in Access Bank UK Annual Report FY2019 (text search, 2026-09-19); FY2020 Pillar 3 (Dec-19 comparatives) has none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: No MREL disclosure (numeric or qualitative) or UK KM2 template found in any year's Pillar 3 report - not explicitly stated as an exemption, but consistent with the Bank's small size relative to typical MREL-in-scope thresholds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="234" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
+FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
+FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
+FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
+FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
+FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
+FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
+FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
+SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="403" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
+For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).
+NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9437,6 +9594,300 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="63" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The Access Bank UK Limited — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Pre-tax return on average shareholders' equity (as published)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>25.83%</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="312" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: TWO KINDS OF FIGURE, NEVER MERGED. The rows above are not one series. The 'Return on equity/assets' rows are THIS PROJECT'S OWN ARITHMETIC on the figures printed on this workbook's statement sheets. The rows marked '(as published)' are the bank's own published ratios, quoted verbatim, each struck on the bank's own definition - which differs from bank to bank and usually from ours, most often in whether the numerator is before or after tax and whether the denominator is average, opening or year-end equity, tangible equity or required equity. They are not averaged, reconciled, or substituted for one another, and where they disagree both stand: the disagreement is the finding.
+THE BANK'S OWN DEFINITIONS, VERBATIM. Pre-tax return on average shareholders' equity: “Return on average shareholders' equity is calculated as the profit before tax for the year divided by the average of the opening and closing shareholders' funds for the year.”
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return.
+FY2019 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2019 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2019 because it needs only the closing balance.
+WHY SOME CELLS SAY 'NOT COMPUTED'. Every year above is marked 'Not computed' rather than given a number, and the reason is a unit problem, not a missing figure. This workbook's statement sheets print (£'000, conv. from USD): the figures were converted from the bank's reporting currency on this project's standing convention, which converts BALANCE SHEET stocks at the financial year-end SPOT rate and PROFIT AND LOSS flows at that year's AVERAGE rate - the right treatment for each statement taken on its own. A ratio struck ACROSS the two therefore divides a figure converted at one rate by a figure converted at another. Both sides are labelled in the same currency, so such a ratio looks sound and is self-consistent on every check this project runs, but it carries the whole spot-versus-average spread - on recent years a bias of roughly two per cent of the ratio, changing sign from year to year, so it distorts the trend as well as the level. The house rule is that a ratio cancels its unit only if both sides share it; where they do not, the honest output is a refusal rather than a number with a caveat attached. A reader who wants these ratios should strike them on the bank's own figures in its own reporting currency, where both sides do share a basis. (scripts/profitability_fx_basis.py records the basis verdict for every converted workbook in this corpus, and why that verdict cannot be read off the page or detected in the code.)
+FIGURES THE BANK PUBLISHED ONLY AS A LATER EDITION'S COMPARATIVE, AND WHY THEY ARE NOT IN THE CELLS ABOVE. FY2022 Pre-tax return on average shareholders' equity 13.47%. Each year's cell carries what that year's OWN annual report printed. A comparative restated in a later edition is a different claim - it may rest on a revised definition, a restated perimeter or a corrected prior figure - so it is recorded here rather than substituted into the year it refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit after tax expense for the year” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from The Access Bank UK Limited's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The '(as published)' rows are quoted verbatim from The Access Bank UK Limited's own disclosures and are recorded, with the exact document, page and verification state for each, in research/profitability/published_returns.jsonl under ‘ACCESS BANK UK’.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A11:H11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10263,152 +10714,6 @@
   <mergeCells count="2">
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A42:G42"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Access Bank UK Limited — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000 (conv. from USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - no Pillar 3 edition; the Annual Report's Capital Resources table prints Tier 1 only</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>599900.9</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>531687.1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>402448.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>279437.2</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>248093.1</v>
-      </c>
-    </row>
-    <row r="5" ht="65" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%. FY2025 is therefore BLANK on this sheet: the Annual Report's Capital Resources table builds to a single 'Total regulatory capital' under the heading 'Tier one capital' and prints no CET1 amount, and no FY2025 Pillar 3 edition exists. Subtracting the convertible notes from Tier 1 to manufacture a CET1 figure is refused - it would not reproduce the Bank's own 11.78% ratio and is not a disclosure the Bank made.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="234" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - The Access Bank UK Limited Pillar 3 Disclosures (UK KM1 - Key Metrics template, or the equivalent UK CC1/LR2 tables for FY2020/FY2021 which pre-date the Bank's KM1 template), converted from USD to £ where a $ amount (see FX conversion note on the Cash Flow Statement sheet; % ratios are unconverted):
-FY2023 &amp; FY2022: Pillar 3 Disclosures 2023, p.6 (Section 1.7, Key Metrics) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/PIllar-3-2023.pdf
-FY2021 (capital/leverage): Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/10/PILLAR-3-DISCLOSURES-2021-Final.pdf
-FY2021 (LCR/NSFR) &amp; FY2020 (capital/leverage): Pillar 3 Disclosures 2022, p.6-7 (Section 1.7 comparative column) &amp; Pillar 3 Disclosures 2021, p.15 (UK CC1) &amp; p.21 (LR2) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2024/01/PILLAR-3-DISCLOSURES-2022-Final.pdf
-FY2019: Pillar 3 Disclosures 2020, p.6 (Section 1.7 FY2019 comparative) and p.17/p.20 (Pillar 1 / leverage comparatives) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2022/06/PILLAR-3-DISCLOSURES-2020-Clean.pdf
-FY2025 (Tier 1 / Total capital amount): Report &amp; Financial Statements 2025, p.81, Note 28g 'Capital management', 'Capital Resources' table, Bank 31 December 2025 column - Total regulatory capital $788,303 thousand - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
-FY2025 (CET1, Tier 1 and LCR ratios): Report &amp; Financial Statements 2025, p.4, Key Performance Indicators table, Bank 2025 column - CET1 Capital Ratio 11.78%, Tier 1 Capital Ratio 19.27%, Liquidity Coverage Ratio 199.46% - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2026/06/AccessBank_AR2025_Financials_web.pdf
-FY2024 (capital amounts): Report &amp; Financial Statements 2024, p.59, Note 27g 'Capital management (Bank)', 'Capital Resources' table - Total tier 1 capital / Total regulatory capital $750,775,693 (shown here as 750,776 $'000 before conversion) - https://www.theaccessbankukltd.co.uk/wp-content/uploads/2025/06/AccessBank_AR2024_Financials-AW.pdf
-SOURCE DEFECT, REPRODUCED NOT CORRECTED: the FY2025 edition's Note 28g narrative says 'Total regulatory capital as at 31 December 2025 including 2025 profit after tax was $793,036 thousand (2024: $750,776 thousand) for the Bank', while the itemised Capital Resources table immediately below it foots to $788,303 thousand (2024: $750,775). The two disagree by $4,733 thousand for 2025 and by rounding only for 2024. The TABLE figure is used here because it is the build-up the Bank shows its working for, and because the FY2024 column above was taken from the equivalent table in the previous edition; the narrative's number is recorded rather than reconciled away.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="286" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-NO FY2024 AND NO FY2025 PILLAR 3 DISCLOSURES DOCUMENT EXISTS - and that finding is now written INTO the FY2025/FY2024 cells of KM1, Total RWAs, RWA Breakdown, Leverage Ratio, NSFR and (FY2025) CET1 Capital, not only into these notes, because a note is invisible to the coverage census and those columns otherwise read as untouched gaps. The evidence is unchanged and is set out immediately below. Independently re-confirmed a third time on 18 September 2026 in the gap-fill round: the 'Our Reports' page was re-fetched with a browser User-Agent over HTTP/1.1 (HTTP 200, text/html, 197,098 bytes), every .pdf href parsed, and it still carries exactly one Pillar 3 entry - 'Pillar 3 Disclosures 2023' at .../2025/06/PIllar-3-2023.pdf - beside 'Annual Report 2025' and 'Report and Financial Statements 2025'; a fresh Wayback CDX sweep of the domain filtered on 'pillar' still returns exactly five documents, newest the 2023 edition; and the WordPress REST media endpoint is still closed (HTTP 401, 'itsec_rest_api_access_restricted') on both /wp-json/wp/v2/media and the ?rest_route= form. Re-verified 18 September 2026 against the Bank's OWN site: its 'Our Reports' page (https://www.theaccessbankukltd.co.uk/about-us/our-reports/) carries exactly one Pillar 3 entry, 'Pillar 3 Disclosures 2023', while the same page was already carrying the FY2025 Annual Report and FY2025 Report &amp; Financial Statements - so the page is current and the Pillar 3 series is what has stopped, not our reading of it. THE PROXY IS NO LONGER NEEDED AND THE 403 IS NOT A REAL BLOCK (established 2026-09-18, second pass, and recorded because the same wrong conclusion will otherwise be drawn again): the page returns 403 to a plain curl, to curl -L, and to curl --http1.1 -L, but returns HTTP 200 with 197,459 bytes of real HTML as soon as a browser User-Agent and an Accept: text/html header are sent over HTTP/1.1. No cookie warm-up is required (one was tried and changed nothing). Cloudflare here is filtering on request HEADERS, not challenging the client. The page was re-read that way, directly from the Bank's own host with no intermediary, and every .pdf href extracted - 25 documents, of which EXACTLY ONE is a Pillar 3 ('.../2025/06/PIllar-3-2023.pdf'), alongside Annual Reports running from 2011 to 2025. That is the same result the proxy gave, now on first-hand evidence. The Bank's WordPress REST media endpoint, which would have listed unlinked uploads too, is closed (HTTP 401, 'itsec_rest_api_access_restricted'), so the reports page is the best enumeration available. A Wayback CDX sweep of the whole domain filtered on 'pillar' returns exactly five documents, the newest still the 2023 edition, and 56 further plausible 2024/2025 filenames probed under the Bank's /wp-content/uploads/ CDN (2025/06, 2025/07, 2025/12, 2026/01, 2026/05, 2026/06, 2026/07 folders) all returned non-200. Three independent routes agree. Publication lag for the next look: the Bank published its FY2025 Annual Report in June 2026 (signed 23 April 2026) and its 2023 Pillar 3 in the 2025/06 folder, i.e. its Pillar 3 has been running roughly 18 months behind year-end, so a FY2024 edition would already be overdue and a FY2025 one would not be expected before mid-2027.
-For FY2024 and FY2025 the Annual Report substitutes ONLY where the basis is verified identical. The AR's capital table is the same basis as the Pillar 3: the FY2024 edition's FY2023 comparative of $676,943,850 reproduces the FY2023 Pillar 3 CET1/Tier 1/Total capital figure of 676,944 $'000 EXACTLY, and the note confirms 'the Bank's regulatory capital consists only of Tier 1 capital'. The AR's Tier 1 Capital Ratio (20.18% for FY2024) likewise ties to the Pillar 3 basis (its FY2023 figure, 22.38%, matches the workbook's 22.4%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="169" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-NOT substituted for FY2024 or FY2025, and left blank rather than derived: Total RWAs (neither Annual Report gives an RWA figure; back-solving $750,775,693 / 20.18% is refused because the ratio is rounded to 2dp, which spans an RWA range of roughly $3,719.5m-$3,721.3m, and the same objection applies to $788,303k / 19.27%); Leverage Ratio (neither AR discloses a leverage ratio or a leverage exposure measure - total assets is NOT the exposure measure, which includes off-balance-sheet items); and NSFR (neither AR contains a quantitative NSFR disclosure - the FY2025 edition mentions the Net Stable Funding Ratio exactly once, in a sentence saying PRA liquidity limits 'are fully met at all times', with no figure; a richness control on the same document returns 33 hits for 'cash flow' and 16 for 'total assets', so that single hit is a fact about the document, not about the extraction). ALL THREE OF THOSE NEGATIVES WERE RE-ESTABLISHED INDEPENDENTLY ON 2026-09-18 against freshly downloaded copies of AccessBank_AR2025_web.pdf (13,090,810 bytes), AccessBank_AR2025_Financials_web.pdf (2,443,676 bytes) and the FY2024 narrative edition AccessBank_AR2024-AW4-1-v2.pdf (4,689,255 bytes), all text-native. In the FY2025 Financials edition (478,570 characters extracted) the phrase 'Risk Weighted Assets' occurs only twice and both are definitional - once in the sentence defining how the Tier 1 Capital Ratio is computed, once in Note 27/28 saying the PRA sets a minimum ratio of regulatory capital to risk-weighted assets - with no RWA AMOUNT printed anywhere; 'leverage ratio' occurs not at all; and the Net Stable Funding Ratio occurs once, in the sentence about PRA liquidity limits being 'fully met at all times'. The Key Performance Indicators table (printed under 'Key Performance Indicators') gives Bank/Group RATIOS only - LCR 199.46/195.71, CET1 ratio 11.78/11.72, Tier 1 ratio 19.27/15.58 - and no denominators. FY2020 LCR/NSFR were not found in any source (narrative-only LCR in the FY2021 Pillar 3 report gives a single FY2021 point figure, no FY2020 comparative; the UK NSFR framework may not yet have covered FY2020) - left blank.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10435,14 +10740,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The Access Bank UK Limited — CET1 Ratio</t>
+          <t>The Access Bank UK Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000 (conv. from USD)</t>
         </is>
       </c>
     </row>
@@ -10486,44 +10791,34 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>11.78%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.18%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>21.88%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>18.40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="39" customHeight="1">
+          <t>Not disclosed - no Pillar 3 edition; the Annual Report's Capital Resources table prints Tier 1 only</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>599900.9</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>531687.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>402448.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>279437.2</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>248093.1</v>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%.</t>
+          <t>Note: FY2025 IS THE FIRST YEAR CET1, TIER 1 AND TOTAL CAPITAL ARE NOT THE SAME NUMBER. For FY2020-FY2024 the Bank held no AT1 and no Tier 2 instruments, so one figure served all three and all three ratios were identical. During 2025 it issued $295.0m of convertible notes, carried as a separate equity component and treated as AT1: its FY2025 capital-management note redefines capital to include 'AT1 capital', and its own KPI table prints a CET1 ratio of 11.78% against a Tier 1 ratio of 19.27%. FY2025 is therefore BLANK on this sheet: the Annual Report's Capital Resources table builds to a single 'Total regulatory capital' under the heading 'Tier one capital' and prints no CET1 amount, and no FY2025 Pillar 3 edition exists. Subtracting the convertible notes from Tier 1 to manufacture a CET1 figure is refused - it would not reproduce the Bank's own 11.78% ratio and is not a disclosure the Bank made.</t>
         </is>
       </c>
     </row>
